--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rae5942358a0d49d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rb5061bc685844cd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5f7b63d437c54c69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rbd378c3cb9d24fb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3ca2093c37ad45c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R3f047ef5a8c94abd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R3a76733645964d32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R94ec7610696b409e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-07T00:43:44.962Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-07T08:19:57.914Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>ec066f78b134a4ab41e86b94133226ce6f6438520682c580b116eb56ed715fc9</x:v>
+        <x:v>682cddfb34b9ba0867e0152518ab5a1ad129de7bbb8828a58f64d23cf072cc71</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>99ba5edfb5f5ec7966456e3ad66285380fe1c91036b9f85ff7846b14c7fd32f2</x:v>
+        <x:v>4139f272a1dd534c1fd927881b22bba0c4b16ce3b4162f405c44d3aab380f491</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1314,7 +1314,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a940d31c6c24f2f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R576d6c5febf847b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2022,7 +2022,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2ecdd70850248fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cb9f076f2824705"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3178,7 +3178,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcd318873e8b45e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6747d8c43dd4b2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3ca2093c37ad45c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R3f047ef5a8c94abd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R3a76733645964d32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R94ec7610696b409e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R02892bb85f77441d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rcc902985c36a4dfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R04fb135491934347"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra7b2fc18f1354610"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -251,7 +251,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G60" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Vertex"/>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-07T08:19:57.914Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-07T12:10:03.268Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>682cddfb34b9ba0867e0152518ab5a1ad129de7bbb8828a58f64d23cf072cc71</x:v>
+        <x:v>43d938ca7f8fb8bab04793528cf39b516a7cfa3e6f752cefca7203bfeafa0aac</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>4139f272a1dd534c1fd927881b22bba0c4b16ce3b4162f405c44d3aab380f491</x:v>
+        <x:v>a162fc27119841a75190b0bc0153cc17495a8bc432ad574a535e8a6799eb9a3d</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1314,7 +1314,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R576d6c5febf847b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a8eaf0d4935480f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1607,8 +1607,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$50,A7,'Route Points'!$F$7:$F$50)</x:f>
-        <x:v>78.099</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$60,A7,'Route Points'!$F$7:$F$60)</x:f>
+        <x:v>69.5751303111792</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
       <x:c r="K7" s="11" t="str">
@@ -1625,7 +1625,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P7" s="8" t="str">
-        <x:v>Concealed wall band above openings; ceiling containment at wing returns</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q7" s="9"/>
       <x:c r="R7" s="9"/>
@@ -1666,8 +1666,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$50,A8,'Route Points'!$F$7:$F$50)</x:f>
-        <x:v>9.544616393605967</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$60,A8,'Route Points'!$F$7:$F$60)</x:f>
+        <x:v>10.048858786281436</x:v>
       </x:c>
       <x:c r="J8" s="11"/>
       <x:c r="K8" s="11" t="str">
@@ -1684,7 +1684,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P8" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
       </x:c>
       <x:c r="Q8" s="9"/>
       <x:c r="R8" s="9"/>
@@ -1727,8 +1727,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$50,A9,'Route Points'!$F$7:$F$50)</x:f>
-        <x:v>2.019</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$60,A9,'Route Points'!$F$7:$F$60)</x:f>
+        <x:v>1.503000000000001</x:v>
       </x:c>
       <x:c r="J9" s="11"/>
       <x:c r="K9" s="11" t="str">
@@ -1745,7 +1745,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P9" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q9" s="9"/>
       <x:c r="R9" s="9"/>
@@ -1788,8 +1788,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$50,A10,'Route Points'!$F$7:$F$50)</x:f>
-        <x:v>2.019</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$60,A10,'Route Points'!$F$7:$F$60)</x:f>
+        <x:v>1.503000000000001</x:v>
       </x:c>
       <x:c r="J10" s="11"/>
       <x:c r="K10" s="11" t="str">
@@ -1806,7 +1806,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P10" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q10" s="9"/>
       <x:c r="R10" s="9"/>
@@ -1850,8 +1850,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$50,A11,'Route Points'!$F$7:$F$50)</x:f>
-        <x:v>71.224</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$60,A11,'Route Points'!$F$7:$F$60)</x:f>
+        <x:v>62.10013031117919</x:v>
       </x:c>
       <x:c r="J11" s="11"/>
       <x:c r="K11" s="11" t="str">
@@ -1868,7 +1868,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P11" s="8" t="str">
-        <x:v>Concealed wall band above openings; ceiling containment at wing returns</x:v>
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
       </x:c>
       <x:c r="Q11" s="9"/>
       <x:c r="R11" s="9"/>
@@ -1909,8 +1909,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$50,A12,'Route Points'!$F$7:$F$50)</x:f>
-        <x:v>2.019</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$60,A12,'Route Points'!$F$7:$F$60)</x:f>
+        <x:v>1.503000000000001</x:v>
       </x:c>
       <x:c r="J12" s="11"/>
       <x:c r="K12" s="11" t="str">
@@ -1927,7 +1927,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P12" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q12" s="9"/>
       <x:c r="R12" s="9"/>
@@ -1970,8 +1970,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$50,A13,'Route Points'!$F$7:$F$50)</x:f>
-        <x:v>2.019</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$60,A13,'Route Points'!$F$7:$F$60)</x:f>
+        <x:v>1.503000000000001</x:v>
       </x:c>
       <x:c r="J13" s="11"/>
       <x:c r="K13" s="11" t="str">
@@ -1988,7 +1988,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P13" s="8" t="str">
-        <x:v>Concealed pier / wall drop, local termination</x:v>
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
       </x:c>
       <x:c r="Q13" s="9"/>
       <x:c r="R13" s="9"/>
@@ -2022,7 +2022,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cb9f076f2824705"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0447863441e64029"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2199,14 +2199,14 @@
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
         <x:f>SQRT((C10-C9)^2+(D10-D9)^2+(E10-E9)^2)</x:f>
-        <x:v>2.1699999999999995</x:v>
+        <x:v>2.48</x:v>
       </x:c>
       <x:c r="G10" s="8" t="str">
         <x:v>Current</x:v>
@@ -2223,14 +2223,14 @@
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
         <x:f>SQRT((C11-C10)^2+(D11-D10)^2+(E11-E10)^2)</x:f>
-        <x:v>1.3599999999999999</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G11" s="8" t="str">
         <x:v>Current</x:v>
@@ -2244,17 +2244,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
         <x:f>SQRT((C12-C11)^2+(D12-D11)^2+(E12-E11)^2)</x:f>
-        <x:v>4.314999999999998</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G12" s="8" t="str">
         <x:v>Current</x:v>
@@ -2268,17 +2268,17 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
         <x:f>SQRT((C13-C12)^2+(D13-D12)^2+(E13-E12)^2)</x:f>
-        <x:v>2.484</x:v>
+        <x:v>1.6580000000000004</x:v>
       </x:c>
       <x:c r="G13" s="8" t="str">
         <x:v>Current</x:v>
@@ -2292,17 +2292,17 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
         <x:f>SQRT((C14-C13)^2+(D14-D13)^2+(E14-E13)^2)</x:f>
-        <x:v>3.7600000000000002</x:v>
+        <x:v>4.0600000000000005</x:v>
       </x:c>
       <x:c r="G14" s="8" t="str">
         <x:v>Current</x:v>
@@ -2319,14 +2319,14 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
         <x:f>SQRT((C15-C14)^2+(D15-D14)^2+(E15-E14)^2)</x:f>
-        <x:v>8.875</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G15" s="8" t="str">
         <x:v>Current</x:v>
@@ -2343,14 +2343,14 @@
         <x:v>44.175</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
         <x:f>SQRT((C16-C15)^2+(D16-D15)^2+(E16-E15)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>1.0519999999999996</x:v>
       </x:c>
       <x:c r="G16" s="8" t="str">
         <x:v>Current</x:v>
@@ -2364,17 +2364,17 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>-13.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
         <x:f>SQRT((C17-C16)^2+(D17-D16)^2+(E17-E16)^2)</x:f>
-        <x:v>7.199999999999996</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G17" s="8" t="str">
         <x:v>Current</x:v>
@@ -2388,17 +2388,17 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>43.455</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>6.950412371134024</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
         <x:f>SQRT((C18-C17)^2+(D18-D17)^2+(E18-E17)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>0.12010804821421249</x:v>
       </x:c>
       <x:c r="G18" s="8" t="str">
         <x:v>Current</x:v>
@@ -2412,17 +2412,17 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>40.574999999999996</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>9.269999999999994</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
         <x:f>SQRT((C19-C18)^2+(D19-D18)^2+(E19-E18)^2)</x:f>
-        <x:v>31.5</x:v>
+        <x:v>3.6979571073753776</x:v>
       </x:c>
       <x:c r="G19" s="8" t="str">
         <x:v>Current</x:v>
@@ -2436,17 +2436,17 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
-        <x:v>2.65</x:v>
+        <x:v>37.695</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>6.950412371134018</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
         <x:f>SQRT((C20-C19)^2+(D20-D19)^2+(E20-E19)^2)</x:f>
-        <x:v>2.8249999999999997</x:v>
+        <x:v>3.697957107375376</x:v>
       </x:c>
       <x:c r="G20" s="8" t="str">
         <x:v>Current</x:v>
@@ -2454,23 +2454,23 @@
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
       <x:c r="A21" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+        <x:v>trunk:LC1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B21" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>2.65</x:v>
+        <x:v>37.615</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C21-C20)^2+(D21-D20)^2+(E21-E20)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
       </x:c>
       <x:c r="G21" s="8" t="str">
         <x:v>Current</x:v>
@@ -2478,23 +2478,23 @@
     </x:row>
     <x:row r="22" ht="32" customHeight="1">
       <x:c r="A22" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+        <x:v>trunk:LC1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B22" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
         <x:f>SQRT((C22-C21)^2+(D22-D21)^2+(E22-E21)^2)</x:f>
-        <x:v>1.1846163936059646</x:v>
+        <x:v>0.6400000000000006</x:v>
       </x:c>
       <x:c r="G22" s="8" t="str">
         <x:v>Current</x:v>
@@ -2502,23 +2502,23 @@
     </x:row>
     <x:row r="23" ht="32" customHeight="1">
       <x:c r="A23" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+        <x:v>trunk:LC1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B23" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>36.975</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
         <x:f>SQRT((C23-C22)^2+(D23-D22)^2+(E23-E22)^2)</x:f>
-        <x:v>7.36</x:v>
+        <x:v>1.0519999999999996</x:v>
       </x:c>
       <x:c r="G23" s="8" t="str">
         <x:v>Current</x:v>
@@ -2526,23 +2526,23 @@
     </x:row>
     <x:row r="24" ht="32" customHeight="1">
       <x:c r="A24" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+        <x:v>trunk:LC1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B24" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>5.475</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>6.95</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
         <x:f>SQRT((C24-C23)^2+(D24-D23)^2+(E24-E23)^2)</x:f>
-        <x:v>0.7000000000000002</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="G24" s="8" t="str">
         <x:v>Current</x:v>
@@ -2550,23 +2550,23 @@
     </x:row>
     <x:row r="25" ht="32" customHeight="1">
       <x:c r="A25" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+        <x:v>trunk:LC1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B25" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
         <x:v>2.65</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>6.95</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
         <x:f>SQRT((C25-C24)^2+(D25-D24)^2+(E25-E24)^2)</x:f>
-        <x:v>0.2999999999999998</x:v>
+        <x:v>2.8249999999999997</x:v>
       </x:c>
       <x:c r="G25" s="8" t="str">
         <x:v>Current</x:v>
@@ -2574,16 +2574,16 @@
     </x:row>
     <x:row r="26" ht="32" customHeight="1">
       <x:c r="A26" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+        <x:v>drop:LC1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="B26" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>2.65</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
         <x:v>-7.36</x:v>
@@ -2598,23 +2598,23 @@
     </x:row>
     <x:row r="27" ht="32" customHeight="1">
       <x:c r="A27" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+        <x:v>drop:LC1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="B27" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>4.6</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
         <x:f>SQRT((C27-C26)^2+(D27-D26)^2+(E27-E26)^2)</x:f>
-        <x:v>1.904</x:v>
+        <x:v>1.6888587862814344</x:v>
       </x:c>
       <x:c r="G27" s="8" t="str">
         <x:v>Current</x:v>
@@ -2622,23 +2622,23 @@
     </x:row>
     <x:row r="28" ht="32" customHeight="1">
       <x:c r="A28" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+        <x:v>drop:LC1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="B28" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>4.6</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>-7.245</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
         <x:f>SQRT((C28-C27)^2+(D28-D27)^2+(E28-E27)^2)</x:f>
-        <x:v>0.11500000000000021</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="G28" s="8" t="str">
         <x:v>Current</x:v>
@@ -2646,167 +2646,167 @@
     </x:row>
     <x:row r="29" ht="32" customHeight="1">
       <x:c r="A29" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L158</x:v>
+        <x:v>drop:LC1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="B29" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="n">
+        <x:v>6.95</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="n">
+        <x:f>SQRT((C29-C28)^2+(D29-D28)^2+(E29-E28)^2)</x:f>
+        <x:v>0.7000000000000002</x:v>
+      </x:c>
+      <x:c r="G29" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="32" customHeight="1">
+      <x:c r="A30" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+      </x:c>
+      <x:c r="B30" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="n">
+        <x:v>2.65</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="n">
+        <x:v>6.95</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="n">
+        <x:f>SQRT((C30-C29)^2+(D30-D29)^2+(E30-E29)^2)</x:f>
+        <x:v>0.2999999999999998</x:v>
+      </x:c>
+      <x:c r="G30" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="32" customHeight="1">
+      <x:c r="A31" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+      </x:c>
+      <x:c r="B31" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C29" s="11" t="n">
-        <x:v>34.725</x:v>
-      </x:c>
-      <x:c r="D29" s="11" t="n">
-        <x:v>6.504</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="n">
+      <x:c r="C31" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
-      <x:c r="F29" s="11" t="n">
+      <x:c r="F31" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="32" customHeight="1">
-      <x:c r="A30" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L158</x:v>
-      </x:c>
-      <x:c r="B30" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C30" s="11" t="n">
-        <x:v>34.725</x:v>
-      </x:c>
-      <x:c r="D30" s="11" t="n">
-        <x:v>4.6</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="n">
-        <x:f>SQRT((C30-C29)^2+(D30-D29)^2+(E30-E29)^2)</x:f>
-        <x:v>1.904</x:v>
-      </x:c>
-      <x:c r="G30" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="32" customHeight="1">
-      <x:c r="A31" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L158</x:v>
-      </x:c>
-      <x:c r="B31" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C31" s="11" t="n">
-        <x:v>34.725</x:v>
-      </x:c>
-      <x:c r="D31" s="11" t="n">
-        <x:v>4.6</x:v>
-      </x:c>
-      <x:c r="E31" s="11" t="n">
-        <x:v>-7.245</x:v>
-      </x:c>
-      <x:c r="F31" s="11" t="n">
-        <x:f>SQRT((C31-C30)^2+(D31-D30)^2+(E31-E30)^2)</x:f>
-        <x:v>0.11500000000000021</x:v>
-      </x:c>
       <x:c r="G31" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="32" customHeight="1">
       <x:c r="A32" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>drop:LC1:E1:light:-1:L156</x:v>
       </x:c>
       <x:c r="B32" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C32" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D32" s="11" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="n">
+        <x:f>SQRT((C32-C31)^2+(D32-D31)^2+(E32-E31)^2)</x:f>
+        <x:v>1.3880000000000008</x:v>
+      </x:c>
+      <x:c r="G32" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="32" customHeight="1">
+      <x:c r="A33" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+      </x:c>
+      <x:c r="B33" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="n">
+        <x:v>-7.245</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="n">
+        <x:f>SQRT((C33-C32)^2+(D33-D32)^2+(E33-E32)^2)</x:f>
+        <x:v>0.11500000000000021</x:v>
+      </x:c>
+      <x:c r="G33" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="32" customHeight="1">
+      <x:c r="A34" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L158</x:v>
+      </x:c>
+      <x:c r="B34" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C32" s="11" t="n">
-        <x:v>48.895</x:v>
-      </x:c>
-      <x:c r="D32" s="11" t="n">
-        <x:v>1.85</x:v>
-      </x:c>
-      <x:c r="E32" s="11" t="n">
-        <x:v>-0.55</x:v>
-      </x:c>
-      <x:c r="F32" s="11" t="n">
+      <x:c r="C34" s="11" t="n">
+        <x:v>34.725</x:v>
+      </x:c>
+      <x:c r="D34" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="32" customHeight="1">
-      <x:c r="A33" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B33" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C33" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D33" s="11" t="n">
-        <x:v>1.85</x:v>
-      </x:c>
-      <x:c r="E33" s="11" t="n">
-        <x:v>-0.55</x:v>
-      </x:c>
-      <x:c r="F33" s="11" t="n">
-        <x:f>SQRT((C33-C32)^2+(D33-D32)^2+(E33-E32)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
-      </x:c>
-      <x:c r="G33" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="32" customHeight="1">
-      <x:c r="A34" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B34" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C34" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D34" s="11" t="n">
-        <x:v>1.85</x:v>
-      </x:c>
-      <x:c r="E34" s="11" t="n">
-        <x:v>-2.24</x:v>
-      </x:c>
-      <x:c r="F34" s="11" t="n">
-        <x:f>SQRT((C34-C33)^2+(D34-D33)^2+(E34-E33)^2)</x:f>
-        <x:v>1.6900000000000002</x:v>
-      </x:c>
       <x:c r="G34" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="32" customHeight="1">
       <x:c r="A35" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>drop:LC1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B35" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.6</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
         <x:f>SQRT((C35-C34)^2+(D35-D34)^2+(E35-E34)^2)</x:f>
-        <x:v>2.1699999999999995</x:v>
+        <x:v>1.3880000000000008</x:v>
       </x:c>
       <x:c r="G35" s="8" t="str">
         <x:v>Current</x:v>
@@ -2814,23 +2814,23 @@
     </x:row>
     <x:row r="36" ht="32" customHeight="1">
       <x:c r="A36" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>drop:LC1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B36" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>4.6</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-7.245</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
         <x:f>SQRT((C36-C35)^2+(D36-D35)^2+(E36-E35)^2)</x:f>
-        <x:v>1.3599999999999999</x:v>
+        <x:v>0.11500000000000021</x:v>
       </x:c>
       <x:c r="G36" s="8" t="str">
         <x:v>Current</x:v>
@@ -2841,20 +2841,20 @@
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B37" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>4.02</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:f>SQRT((C37-C36)^2+(D37-D36)^2+(E37-E36)^2)</x:f>
-        <x:v>4.314999999999998</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G37" s="8" t="str">
         <x:v>Current</x:v>
@@ -2865,20 +2865,20 @@
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B38" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>-3.6</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
         <x:f>SQRT((C38-C37)^2+(D38-D37)^2+(E38-E37)^2)</x:f>
-        <x:v>2.484</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G38" s="8" t="str">
         <x:v>Current</x:v>
@@ -2889,20 +2889,20 @@
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B39" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
-        <x:v>53.05</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
         <x:f>SQRT((C39-C38)^2+(D39-D38)^2+(E39-E38)^2)</x:f>
-        <x:v>10.96</x:v>
+        <x:v>1.6900000000000002</x:v>
       </x:c>
       <x:c r="G39" s="8" t="str">
         <x:v>Current</x:v>
@@ -2913,20 +2913,20 @@
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B40" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
         <x:f>SQRT((C40-C39)^2+(D40-D39)^2+(E40-E39)^2)</x:f>
-        <x:v>8.875</x:v>
+        <x:v>2.48</x:v>
       </x:c>
       <x:c r="G40" s="8" t="str">
         <x:v>Current</x:v>
@@ -2937,20 +2937,20 @@
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B41" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>13.24</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
         <x:f>SQRT((C41-C40)^2+(D41-D40)^2+(E41-E40)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G41" s="8" t="str">
         <x:v>Current</x:v>
@@ -2961,20 +2961,20 @@
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B42" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>13.24</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
         <x:f>SQRT((C42-C41)^2+(D42-D41)^2+(E42-E41)^2)</x:f>
-        <x:v>7.199999999999996</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G42" s="8" t="str">
         <x:v>Current</x:v>
@@ -2985,20 +2985,20 @@
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B43" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
         <x:f>SQRT((C43-C42)^2+(D43-D42)^2+(E43-E42)^2)</x:f>
-        <x:v>5.88</x:v>
+        <x:v>1.6580000000000004</x:v>
       </x:c>
       <x:c r="G43" s="8" t="str">
         <x:v>Current</x:v>
@@ -3009,20 +3009,20 @@
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B44" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
         <x:f>SQRT((C44-C43)^2+(D44-D43)^2+(E44-E43)^2)</x:f>
-        <x:v>20.25</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G44" s="8" t="str">
         <x:v>Current</x:v>
@@ -3030,155 +3030,395 @@
     </x:row>
     <x:row r="45" ht="32" customHeight="1">
       <x:c r="A45" s="8" t="str">
-        <x:v>drop:LC1:E1:light:1:L157</x:v>
+        <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B45" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>6.504</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
+        <x:f>SQRT((C45-C44)^2+(D45-D44)^2+(E45-E44)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
+      </x:c>
+      <x:c r="G45" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="32" customHeight="1">
+      <x:c r="A46" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B46" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C46" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D46" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E46" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="n">
+        <x:f>SQRT((C46-C45)^2+(D46-D45)^2+(E46-E45)^2)</x:f>
+        <x:v>1.0519999999999996</x:v>
+      </x:c>
+      <x:c r="G46" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="32" customHeight="1">
+      <x:c r="A47" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B47" s="8" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C47" s="11" t="n">
+        <x:v>43.535</x:v>
+      </x:c>
+      <x:c r="D47" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E47" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F47" s="11" t="n">
+        <x:f>SQRT((C47-C46)^2+(D47-D46)^2+(E47-E46)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G47" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="32" customHeight="1">
+      <x:c r="A48" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B48" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C48" s="11" t="n">
+        <x:v>43.455</x:v>
+      </x:c>
+      <x:c r="D48" s="11" t="n">
+        <x:v>6.950412371134024</x:v>
+      </x:c>
+      <x:c r="E48" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F48" s="11" t="n">
+        <x:f>SQRT((C48-C47)^2+(D48-D47)^2+(E48-E47)^2)</x:f>
+        <x:v>0.12010804821421249</x:v>
+      </x:c>
+      <x:c r="G48" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="32" customHeight="1">
+      <x:c r="A49" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B49" s="8" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C49" s="11" t="n">
+        <x:v>40.574999999999996</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="n">
+        <x:v>9.269999999999994</x:v>
+      </x:c>
+      <x:c r="E49" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F49" s="11" t="n">
+        <x:f>SQRT((C49-C48)^2+(D49-D48)^2+(E49-E48)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
+      </x:c>
+      <x:c r="G49" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="32" customHeight="1">
+      <x:c r="A50" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B50" s="8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C50" s="11" t="n">
+        <x:v>37.695</x:v>
+      </x:c>
+      <x:c r="D50" s="11" t="n">
+        <x:v>6.950412371134018</x:v>
+      </x:c>
+      <x:c r="E50" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F50" s="11" t="n">
+        <x:f>SQRT((C50-C49)^2+(D50-D49)^2+(E50-E49)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
+      </x:c>
+      <x:c r="G50" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="32" customHeight="1">
+      <x:c r="A51" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B51" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C51" s="11" t="n">
+        <x:v>37.615</x:v>
+      </x:c>
+      <x:c r="D51" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E51" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F51" s="11" t="n">
+        <x:f>SQRT((C51-C50)^2+(D51-D50)^2+(E51-E50)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
+      </x:c>
+      <x:c r="G51" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="32" customHeight="1">
+      <x:c r="A52" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B52" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C52" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D52" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E52" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F52" s="11" t="n">
+        <x:f>SQRT((C52-C51)^2+(D52-D51)^2+(E52-E51)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G52" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="32" customHeight="1">
+      <x:c r="A53" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B53" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C53" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D53" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E53" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F53" s="11" t="n">
+        <x:f>SQRT((C53-C52)^2+(D53-D52)^2+(E53-E52)^2)</x:f>
+        <x:v>1.0519999999999996</x:v>
+      </x:c>
+      <x:c r="G53" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="32" customHeight="1">
+      <x:c r="A54" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B54" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C54" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D54" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E54" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F54" s="11" t="n">
+        <x:f>SQRT((C54-C53)^2+(D54-D53)^2+(E54-E53)^2)</x:f>
+        <x:v>20.25</x:v>
+      </x:c>
+      <x:c r="G54" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="32" customHeight="1">
+      <x:c r="A55" s="8" t="str">
+        <x:v>drop:LC1:E1:light:1:L157</x:v>
+      </x:c>
+      <x:c r="B55" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C55" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D55" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E55" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F55" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G45" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="32" customHeight="1">
-      <x:c r="A46" s="8" t="str">
+      <x:c r="G55" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="32" customHeight="1">
+      <x:c r="A56" s="8" t="str">
         <x:v>drop:LC1:E1:light:1:L157</x:v>
       </x:c>
-      <x:c r="B46" s="8" t="n">
+      <x:c r="B56" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C46" s="11" t="n">
+      <x:c r="C56" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
-      <x:c r="D46" s="11" t="n">
+      <x:c r="D56" s="11" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="E46" s="11" t="n">
+      <x:c r="E56" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F46" s="11" t="n">
-        <x:f>SQRT((C46-C45)^2+(D46-D45)^2+(E46-E45)^2)</x:f>
-        <x:v>1.904</x:v>
-      </x:c>
-      <x:c r="G46" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="32" customHeight="1">
-      <x:c r="A47" s="8" t="str">
+      <x:c r="F56" s="11" t="n">
+        <x:f>SQRT((C56-C55)^2+(D56-D55)^2+(E56-E55)^2)</x:f>
+        <x:v>1.3880000000000008</x:v>
+      </x:c>
+      <x:c r="G56" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="32" customHeight="1">
+      <x:c r="A57" s="8" t="str">
         <x:v>drop:LC1:E1:light:1:L157</x:v>
       </x:c>
-      <x:c r="B47" s="8" t="n">
+      <x:c r="B57" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C47" s="11" t="n">
+      <x:c r="C57" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
-      <x:c r="D47" s="11" t="n">
+      <x:c r="D57" s="11" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="E47" s="11" t="n">
+      <x:c r="E57" s="11" t="n">
         <x:v>7.245</x:v>
       </x:c>
-      <x:c r="F47" s="11" t="n">
-        <x:f>SQRT((C47-C46)^2+(D47-D46)^2+(E47-E46)^2)</x:f>
+      <x:c r="F57" s="11" t="n">
+        <x:f>SQRT((C57-C56)^2+(D57-D56)^2+(E57-E56)^2)</x:f>
         <x:v>0.11500000000000021</x:v>
       </x:c>
-      <x:c r="G47" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" ht="32" customHeight="1">
-      <x:c r="A48" s="8" t="str">
+      <x:c r="G57" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="32" customHeight="1">
+      <x:c r="A58" s="8" t="str">
         <x:v>drop:LC1:E1:light:1:L159</x:v>
       </x:c>
-      <x:c r="B48" s="8" t="n">
+      <x:c r="B58" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C48" s="11" t="n">
+      <x:c r="C58" s="11" t="n">
         <x:v>34.725</x:v>
       </x:c>
-      <x:c r="D48" s="11" t="n">
-        <x:v>6.504</x:v>
-      </x:c>
-      <x:c r="E48" s="11" t="n">
+      <x:c r="D58" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E58" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F48" s="11" t="n">
+      <x:c r="F58" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G48" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="32" customHeight="1">
-      <x:c r="A49" s="8" t="str">
+      <x:c r="G58" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="32" customHeight="1">
+      <x:c r="A59" s="8" t="str">
         <x:v>drop:LC1:E1:light:1:L159</x:v>
       </x:c>
-      <x:c r="B49" s="8" t="n">
+      <x:c r="B59" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C49" s="11" t="n">
+      <x:c r="C59" s="11" t="n">
         <x:v>34.725</x:v>
       </x:c>
-      <x:c r="D49" s="11" t="n">
+      <x:c r="D59" s="11" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="E49" s="11" t="n">
+      <x:c r="E59" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F49" s="11" t="n">
-        <x:f>SQRT((C49-C48)^2+(D49-D48)^2+(E49-E48)^2)</x:f>
-        <x:v>1.904</x:v>
-      </x:c>
-      <x:c r="G49" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="32" customHeight="1">
-      <x:c r="A50" s="8" t="str">
+      <x:c r="F59" s="11" t="n">
+        <x:f>SQRT((C59-C58)^2+(D59-D58)^2+(E59-E58)^2)</x:f>
+        <x:v>1.3880000000000008</x:v>
+      </x:c>
+      <x:c r="G59" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="32" customHeight="1">
+      <x:c r="A60" s="8" t="str">
         <x:v>drop:LC1:E1:light:1:L159</x:v>
       </x:c>
-      <x:c r="B50" s="8" t="n">
+      <x:c r="B60" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C50" s="11" t="n">
+      <x:c r="C60" s="11" t="n">
         <x:v>34.725</x:v>
       </x:c>
-      <x:c r="D50" s="11" t="n">
+      <x:c r="D60" s="11" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="E50" s="11" t="n">
+      <x:c r="E60" s="11" t="n">
         <x:v>7.245</x:v>
       </x:c>
-      <x:c r="F50" s="11" t="n">
-        <x:f>SQRT((C50-C49)^2+(D50-D49)^2+(E50-E49)^2)</x:f>
+      <x:c r="F60" s="11" t="n">
+        <x:f>SQRT((C60-C59)^2+(D60-D59)^2+(E60-E59)^2)</x:f>
         <x:v>0.11500000000000021</x:v>
       </x:c>
-      <x:c r="G50" s="8" t="str">
+      <x:c r="G60" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G7:G50">
+  <x:conditionalFormatting sqref="G7:G60">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6747d8c43dd4b2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R599ea06ebdbd4f5b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R02892bb85f77441d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rcc902985c36a4dfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R04fb135491934347"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra7b2fc18f1354610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd9dd1e795f9c414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Ref573cea4a904269"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rad35017e75604047"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rdbf2523a8cf74a19"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-07T12:10:03.268Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-08T22:16:25.645Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>43d938ca7f8fb8bab04793528cf39b516a7cfa3e6f752cefca7203bfeafa0aac</x:v>
+        <x:v>53ff13ffefd2679cbf8d12a1e21bde566f40af08275ae4f0ff95823f70ea1b77</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>a162fc27119841a75190b0bc0153cc17495a8bc432ad574a535e8a6799eb9a3d</x:v>
+        <x:v>c883a38876b1d2b04788046ec5e1d87651113aa8dbfeb0f5415ba0b829f004ab</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1314,7 +1314,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a8eaf0d4935480f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R750f04ad449348f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2022,7 +2022,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0447863441e64029"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91dff2efb0bc4725"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3418,7 +3418,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R599ea06ebdbd4f5b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8854d30902b54a1e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd9dd1e795f9c414d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Ref573cea4a904269"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rad35017e75604047"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rdbf2523a8cf74a19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4d0fa7501f18408b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Ra7b8a641b9154daf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R986d2ab6baf34da2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R416d61f857fd4a36"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-08T22:16:25.645Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-09T01:06:21.478Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>53ff13ffefd2679cbf8d12a1e21bde566f40af08275ae4f0ff95823f70ea1b77</x:v>
+        <x:v>d4067e8bb027f3bb435cc6fee67c0fc1d0e462a2d8802a6ada0bb37df793ab52</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>c883a38876b1d2b04788046ec5e1d87651113aa8dbfeb0f5415ba0b829f004ab</x:v>
+        <x:v>e2130aeffb518d934149fa35c32d858856db06e804d9cb98aac4f1896cd3b761</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1314,7 +1314,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R750f04ad449348f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R038d71e02f11483e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2022,7 +2022,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91dff2efb0bc4725"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55502157f2d643ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3418,7 +3418,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8854d30902b54a1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f692b0d4c5742a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4d0fa7501f18408b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Ra7b8a641b9154daf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R986d2ab6baf34da2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R416d61f857fd4a36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R50146e75d7e84257"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R629ddd94782c4dbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R521bbf8730974349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1ce6570f01324d7c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-09T01:06:21.478Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-09T01:31:17.233Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>d4067e8bb027f3bb435cc6fee67c0fc1d0e462a2d8802a6ada0bb37df793ab52</x:v>
+        <x:v>80b0da7d5afe7ebc6ad40230d4100ad0f2b4b395a8a63b44da5d741ccd64e05d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e2130aeffb518d934149fa35c32d858856db06e804d9cb98aac4f1896cd3b761</x:v>
+        <x:v>78a1f21a5458fc451b1fadb227a547feb6afa62226cd02a3db53eaacd4fe65ce</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1314,7 +1314,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R038d71e02f11483e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7665eb084d74aa7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2022,7 +2022,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55502157f2d643ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbe1d32bc11c4a4b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3418,7 +3418,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f692b0d4c5742a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b9420857c334b88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R50146e75d7e84257"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R629ddd94782c4dbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R521bbf8730974349"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1ce6570f01324d7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R8634ddbfb5ec4aaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rcdcf98167f73499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5d819b80c62647d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R743b2cd5fac048c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-09T01:31:17.233Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-09T03:17:36.119Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>80b0da7d5afe7ebc6ad40230d4100ad0f2b4b395a8a63b44da5d741ccd64e05d</x:v>
+        <x:v>f58ecb8c7e66db5f5a9c359a0501f9a7ff3253b9cb9664b76918bdc2f036e05a</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>78a1f21a5458fc451b1fadb227a547feb6afa62226cd02a3db53eaacd4fe65ce</x:v>
+        <x:v>1646f19d4f8b80070625f5fb407f54d11abbea5d7ecb7c88a4a2534f18542306</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1314,7 +1314,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7665eb084d74aa7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0df1101d44c34471"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2022,7 +2022,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbe1d32bc11c4a4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09c9c8e2a8de4c47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3418,7 +3418,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b9420857c334b88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31c53e96d2b54268"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R8634ddbfb5ec4aaf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rcdcf98167f73499e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R5d819b80c62647d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R743b2cd5fac048c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4141ac97736d4bc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R890ebeb3bdac4472"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rb1262e2df6094241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra6432967daba49bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -217,7 +217,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ElectricalLineRegister" displayName="ElectricalLineRegister" ref="A6:Z13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ElectricalLineRegister" displayName="ElectricalLineRegister" ref="A6:Z20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Name"/>
@@ -251,7 +251,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G60" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G114" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Vertex"/>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-09T03:17:36.119Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-09T04:54:03.663Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -504,7 +504,7 @@
         <x:v>Current routes</x:v>
       </x:c>
       <x:c r="B6" s="16" t="n">
-        <x:f>COUNTIFS('Electrical Lines'!$Y$7:$Y$13,"Current")</x:f>
+        <x:f>COUNTIFS('Electrical Lines'!$Y$7:$Y$20,"Current")</x:f>
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -513,8 +513,8 @@
         <x:v>Retired equipment / routes</x:v>
       </x:c>
       <x:c r="B7" s="16" t="n">
-        <x:f>COUNTIFS(Equipment!$AA$7:$AA$11,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$13,"Retired")</x:f>
-        <x:v>0</x:v>
+        <x:f>COUNTIFS(Equipment!$AA$7:$AA$11,"Retired")+COUNTIFS('Electrical Lines'!$Y$7:$Y$20,"Retired")</x:f>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>f58ecb8c7e66db5f5a9c359a0501f9a7ff3253b9cb9664b76918bdc2f036e05a</x:v>
+        <x:v>e8b0d45e0c5518ca0cc64c1fa511adc8ba03ba31bef6d46426ff3c0c3e699bab</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +578,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>1646f19d4f8b80070625f5fb407f54d11abbea5d7ecb7c88a4a2534f18542306</x:v>
+        <x:v>e25c59374b1948a67cdb0ee5bed0beb9884da65931cb92b8dc2af738d4ae1e28</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1012,7 +1012,7 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="AB7" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+        <x:v>drop:DB1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="AC7" s="8" t="str">
         <x:v>{"dim":1}</x:v>
@@ -1081,7 +1081,7 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="AB8" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+        <x:v>drop:DB1:E1:light:-1:L156</x:v>
       </x:c>
       <x:c r="AC8" s="8" t="str">
         <x:v>{"dim":1}</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="AB9" s="8" t="str">
-        <x:v>drop:LC1:E1:light:1:L157</x:v>
+        <x:v>drop:DB1:E1:light:1:L157</x:v>
       </x:c>
       <x:c r="AC9" s="8" t="str">
         <x:v>{"dim":1}</x:v>
@@ -1219,7 +1219,7 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="AB10" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L158</x:v>
+        <x:v>drop:DB1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="AC10" s="8" t="str">
         <x:v>{"dim":1}</x:v>
@@ -1288,7 +1288,7 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="AB11" s="8" t="str">
-        <x:v>drop:LC1:E1:light:1:L159</x:v>
+        <x:v>drop:DB1:E1:light:1:L159</x:v>
       </x:c>
       <x:c r="AC11" s="8" t="str">
         <x:v>{"dim":1}</x:v>
@@ -1314,7 +1314,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0df1101d44c34471"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63d13117f67b4d03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1581,13 +1581,13 @@
     </x:row>
     <x:row r="7" ht="90" customHeight="1">
       <x:c r="A7" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
         <x:v>E1 · B · circuit trunk</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
-        <x:v>LC1</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="D7" s="8" t="str">
         <x:v>L155
@@ -1607,8 +1607,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$60,A7,'Route Points'!$F$7:$F$60)</x:f>
-        <x:v>69.5751303111792</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A7,'Route Points'!$F$7:$F$114)</x:f>
+        <x:v>68.67513031117919</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
       <x:c r="K7" s="11" t="str">
@@ -1642,13 +1642,13 @@
     </x:row>
     <x:row r="8" ht="90" customHeight="1">
       <x:c r="A8" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+        <x:v>drop:DB1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
         <x:v>E1 → Exit sign · main doors</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>LC1</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
         <x:v>L155</x:v>
@@ -1666,7 +1666,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$60,A8,'Route Points'!$F$7:$F$60)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A8,'Route Points'!$F$7:$F$114)</x:f>
         <x:v>10.048858786281436</x:v>
       </x:c>
       <x:c r="J8" s="11"/>
@@ -1698,18 +1698,18 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z8" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="90" customHeight="1">
       <x:c r="A9" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+        <x:v>drop:DB1:E1:light:-1:L156</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
         <x:v>E1 → Exit sign · side door 16.7 · B</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
-        <x:v>LC1</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
         <x:v>L156</x:v>
@@ -1727,7 +1727,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$60,A9,'Route Points'!$F$7:$F$60)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A9,'Route Points'!$F$7:$F$114)</x:f>
         <x:v>1.503000000000001</x:v>
       </x:c>
       <x:c r="J9" s="11"/>
@@ -1759,18 +1759,18 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z9" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="90" customHeight="1">
       <x:c r="A10" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L158</x:v>
+        <x:v>drop:DB1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
         <x:v>E1 → Exit sign · side door 34.7 · B</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>LC1</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
         <x:v>L158</x:v>
@@ -1788,7 +1788,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$60,A10,'Route Points'!$F$7:$F$60)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A10,'Route Points'!$F$7:$F$114)</x:f>
         <x:v>1.503000000000001</x:v>
       </x:c>
       <x:c r="J10" s="11"/>
@@ -1820,18 +1820,18 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z10" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="90" customHeight="1">
       <x:c r="A11" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
         <x:v>E1 · H · circuit trunk</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
-        <x:v>LC1</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
         <x:v>L157
@@ -1850,8 +1850,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$60,A11,'Route Points'!$F$7:$F$60)</x:f>
-        <x:v>62.10013031117919</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A11,'Route Points'!$F$7:$F$114)</x:f>
+        <x:v>61.20013031117919</x:v>
       </x:c>
       <x:c r="J11" s="11"/>
       <x:c r="K11" s="11" t="str">
@@ -1885,13 +1885,13 @@
     </x:row>
     <x:row r="12" ht="90" customHeight="1">
       <x:c r="A12" s="8" t="str">
-        <x:v>drop:LC1:E1:light:1:L157</x:v>
+        <x:v>drop:DB1:E1:light:1:L157</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
         <x:v>E1 → Exit sign · side door 16.7 · H</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>LC1</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
         <x:v>L157</x:v>
@@ -1909,7 +1909,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$60,A12,'Route Points'!$F$7:$F$60)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A12,'Route Points'!$F$7:$F$114)</x:f>
         <x:v>1.503000000000001</x:v>
       </x:c>
       <x:c r="J12" s="11"/>
@@ -1941,18 +1941,18 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z12" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="90" customHeight="1">
       <x:c r="A13" s="8" t="str">
-        <x:v>drop:LC1:E1:light:1:L159</x:v>
+        <x:v>drop:DB1:E1:light:1:L159</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
         <x:v>E1 → Exit sign · side door 34.7 · H</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
-        <x:v>LC1</x:v>
+        <x:v>DB1</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
         <x:v>L159</x:v>
@@ -1970,7 +1970,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$60,A13,'Route Points'!$F$7:$F$60)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A13,'Route Points'!$F$7:$F$114)</x:f>
         <x:v>1.503000000000001</x:v>
       </x:c>
       <x:c r="J13" s="11"/>
@@ -2002,27 +2002,453 @@
         <x:v>Current</x:v>
       </x:c>
       <x:c r="Z13" s="8" t="str">
+        <x:v>trunk:DB1:E1:light:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="90" customHeight="1">
+      <x:c r="A14" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>E1 · B · circuit trunk</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="str">
+        <x:v>LC1</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="str">
+        <x:v>L155
+L156
+L158</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="str">
+        <x:v>E1</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="H14" s="8" t="str">
+        <x:v>trunk</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A14,'Route Points'!$F$7:$F$114)</x:f>
+        <x:v>69.5751303111792</x:v>
+      </x:c>
+      <x:c r="J14" s="11"/>
+      <x:c r="K14" s="11" t="str">
+        <x:f>IF(L14="Full home run",I14+J14,"")</x:f>
+      </x:c>
+      <x:c r="L14" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M14" s="13"/>
+      <x:c r="N14" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M14),L14&lt;&gt;"Shared bundle"),IF(L14="Full home run",K14,I14)+M14,"")</x:f>
+      </x:c>
+      <x:c r="O14" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P14" s="8" t="str">
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+      </x:c>
+      <x:c r="Q14" s="9"/>
+      <x:c r="R14" s="9"/>
+      <x:c r="S14" s="13"/>
+      <x:c r="T14" s="9"/>
+      <x:c r="U14" s="9"/>
+      <x:c r="V14" s="9"/>
+      <x:c r="W14" s="9"/>
+      <x:c r="X14" s="9"/>
+      <x:c r="Y14" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z14" s="8"/>
+    </x:row>
+    <x:row r="15" ht="90" customHeight="1">
+      <x:c r="A15" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="str">
+        <x:v>E1 → Exit sign · main doors</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="str">
+        <x:v>LC1</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="str">
+        <x:v>L155</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F15" s="8" t="str">
+        <x:v>E1</x:v>
+      </x:c>
+      <x:c r="G15" s="8" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="H15" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A15,'Route Points'!$F$7:$F$114)</x:f>
+        <x:v>10.048858786281436</x:v>
+      </x:c>
+      <x:c r="J15" s="11"/>
+      <x:c r="K15" s="11" t="str">
+        <x:f>IF(L15="Full home run",I15+J15,"")</x:f>
+      </x:c>
+      <x:c r="L15" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M15" s="13"/>
+      <x:c r="N15" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M15),L15&lt;&gt;"Shared bundle"),IF(L15="Full home run",K15,I15)+M15,"")</x:f>
+      </x:c>
+      <x:c r="O15" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P15" s="8" t="str">
+        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
+      </x:c>
+      <x:c r="Q15" s="9"/>
+      <x:c r="R15" s="9"/>
+      <x:c r="S15" s="13"/>
+      <x:c r="T15" s="9"/>
+      <x:c r="U15" s="9"/>
+      <x:c r="V15" s="9"/>
+      <x:c r="W15" s="9"/>
+      <x:c r="X15" s="9"/>
+      <x:c r="Y15" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z15" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="90" customHeight="1">
+      <x:c r="A16" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+      </x:c>
+      <x:c r="B16" s="8" t="str">
+        <x:v>E1 → Exit sign · side door 16.7 · B</x:v>
+      </x:c>
+      <x:c r="C16" s="8" t="str">
+        <x:v>LC1</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="str">
+        <x:v>L156</x:v>
+      </x:c>
+      <x:c r="E16" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F16" s="8" t="str">
+        <x:v>E1</x:v>
+      </x:c>
+      <x:c r="G16" s="8" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="H16" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A16,'Route Points'!$F$7:$F$114)</x:f>
+        <x:v>1.503000000000001</x:v>
+      </x:c>
+      <x:c r="J16" s="11"/>
+      <x:c r="K16" s="11" t="str">
+        <x:f>IF(L16="Full home run",I16+J16,"")</x:f>
+      </x:c>
+      <x:c r="L16" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M16" s="13"/>
+      <x:c r="N16" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M16),L16&lt;&gt;"Shared bundle"),IF(L16="Full home run",K16,I16)+M16,"")</x:f>
+      </x:c>
+      <x:c r="O16" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P16" s="8" t="str">
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+      </x:c>
+      <x:c r="Q16" s="9"/>
+      <x:c r="R16" s="9"/>
+      <x:c r="S16" s="13"/>
+      <x:c r="T16" s="9"/>
+      <x:c r="U16" s="9"/>
+      <x:c r="V16" s="9"/>
+      <x:c r="W16" s="9"/>
+      <x:c r="X16" s="9"/>
+      <x:c r="Y16" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z16" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="90" customHeight="1">
+      <x:c r="A17" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L158</x:v>
+      </x:c>
+      <x:c r="B17" s="8" t="str">
+        <x:v>E1 → Exit sign · side door 34.7 · B</x:v>
+      </x:c>
+      <x:c r="C17" s="8" t="str">
+        <x:v>LC1</x:v>
+      </x:c>
+      <x:c r="D17" s="8" t="str">
+        <x:v>L158</x:v>
+      </x:c>
+      <x:c r="E17" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F17" s="8" t="str">
+        <x:v>E1</x:v>
+      </x:c>
+      <x:c r="G17" s="8" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="H17" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A17,'Route Points'!$F$7:$F$114)</x:f>
+        <x:v>1.503000000000001</x:v>
+      </x:c>
+      <x:c r="J17" s="11"/>
+      <x:c r="K17" s="11" t="str">
+        <x:f>IF(L17="Full home run",I17+J17,"")</x:f>
+      </x:c>
+      <x:c r="L17" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M17" s="13"/>
+      <x:c r="N17" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M17),L17&lt;&gt;"Shared bundle"),IF(L17="Full home run",K17,I17)+M17,"")</x:f>
+      </x:c>
+      <x:c r="O17" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P17" s="8" t="str">
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+      </x:c>
+      <x:c r="Q17" s="9"/>
+      <x:c r="R17" s="9"/>
+      <x:c r="S17" s="13"/>
+      <x:c r="T17" s="9"/>
+      <x:c r="U17" s="9"/>
+      <x:c r="V17" s="9"/>
+      <x:c r="W17" s="9"/>
+      <x:c r="X17" s="9"/>
+      <x:c r="Y17" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z17" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="90" customHeight="1">
+      <x:c r="A18" s="8" t="str">
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
+      <x:c r="B18" s="8" t="str">
+        <x:v>E1 · H · circuit trunk</x:v>
+      </x:c>
+      <x:c r="C18" s="8" t="str">
+        <x:v>LC1</x:v>
+      </x:c>
+      <x:c r="D18" s="8" t="str">
+        <x:v>L157
+L159</x:v>
+      </x:c>
+      <x:c r="E18" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F18" s="8" t="str">
+        <x:v>E1</x:v>
+      </x:c>
+      <x:c r="G18" s="8" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="H18" s="8" t="str">
+        <x:v>trunk</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A18,'Route Points'!$F$7:$F$114)</x:f>
+        <x:v>62.10013031117919</x:v>
+      </x:c>
+      <x:c r="J18" s="11"/>
+      <x:c r="K18" s="11" t="str">
+        <x:f>IF(L18="Full home run",I18+J18,"")</x:f>
+      </x:c>
+      <x:c r="L18" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M18" s="13"/>
+      <x:c r="N18" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M18),L18&lt;&gt;"Shared bundle"),IF(L18="Full home run",K18,I18)+M18,"")</x:f>
+      </x:c>
+      <x:c r="O18" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P18" s="8" t="str">
+        <x:v>Wall bands above openings; concealed finish-matched soffit crossing over the 9–10 wing opening.</x:v>
+      </x:c>
+      <x:c r="Q18" s="9"/>
+      <x:c r="R18" s="9"/>
+      <x:c r="S18" s="13"/>
+      <x:c r="T18" s="9"/>
+      <x:c r="U18" s="9"/>
+      <x:c r="V18" s="9"/>
+      <x:c r="W18" s="9"/>
+      <x:c r="X18" s="9"/>
+      <x:c r="Y18" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z18" s="8"/>
+    </x:row>
+    <x:row r="19" ht="90" customHeight="1">
+      <x:c r="A19" s="8" t="str">
+        <x:v>drop:LC1:E1:light:1:L157</x:v>
+      </x:c>
+      <x:c r="B19" s="8" t="str">
+        <x:v>E1 → Exit sign · side door 16.7 · H</x:v>
+      </x:c>
+      <x:c r="C19" s="8" t="str">
+        <x:v>LC1</x:v>
+      </x:c>
+      <x:c r="D19" s="8" t="str">
+        <x:v>L157</x:v>
+      </x:c>
+      <x:c r="E19" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F19" s="8" t="str">
+        <x:v>E1</x:v>
+      </x:c>
+      <x:c r="G19" s="8" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="H19" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I19" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A19,'Route Points'!$F$7:$F$114)</x:f>
+        <x:v>1.503000000000001</x:v>
+      </x:c>
+      <x:c r="J19" s="11"/>
+      <x:c r="K19" s="11" t="str">
+        <x:f>IF(L19="Full home run",I19+J19,"")</x:f>
+      </x:c>
+      <x:c r="L19" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M19" s="13"/>
+      <x:c r="N19" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M19),L19&lt;&gt;"Shared bundle"),IF(L19="Full home run",K19,I19)+M19,"")</x:f>
+      </x:c>
+      <x:c r="O19" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P19" s="8" t="str">
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+      </x:c>
+      <x:c r="Q19" s="9"/>
+      <x:c r="R19" s="9"/>
+      <x:c r="S19" s="13"/>
+      <x:c r="T19" s="9"/>
+      <x:c r="U19" s="9"/>
+      <x:c r="V19" s="9"/>
+      <x:c r="W19" s="9"/>
+      <x:c r="X19" s="9"/>
+      <x:c r="Y19" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z19" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="90" customHeight="1">
+      <x:c r="A20" s="8" t="str">
+        <x:v>drop:LC1:E1:light:1:L159</x:v>
+      </x:c>
+      <x:c r="B20" s="8" t="str">
+        <x:v>E1 → Exit sign · side door 34.7 · H</x:v>
+      </x:c>
+      <x:c r="C20" s="8" t="str">
+        <x:v>LC1</x:v>
+      </x:c>
+      <x:c r="D20" s="8" t="str">
+        <x:v>L159</x:v>
+      </x:c>
+      <x:c r="E20" s="8" t="str">
+        <x:v>DB1</x:v>
+      </x:c>
+      <x:c r="F20" s="8" t="str">
+        <x:v>E1</x:v>
+      </x:c>
+      <x:c r="G20" s="8" t="str">
+        <x:v>light</x:v>
+      </x:c>
+      <x:c r="H20" s="8" t="str">
+        <x:v>drop</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="n">
+        <x:f>SUMIF('Route Points'!$A$7:$A$114,A20,'Route Points'!$F$7:$F$114)</x:f>
+        <x:v>1.503000000000001</x:v>
+      </x:c>
+      <x:c r="J20" s="11"/>
+      <x:c r="K20" s="11" t="str">
+        <x:f>IF(L20="Full home run",I20+J20,"")</x:f>
+      </x:c>
+      <x:c r="L20" s="8" t="str">
+        <x:v>Route segment</x:v>
+      </x:c>
+      <x:c r="M20" s="13"/>
+      <x:c r="N20" s="11" t="str">
+        <x:f>IF(AND(ISNUMBER(M20),L20&lt;&gt;"Shared bundle"),IF(L20="Full home run",K20,I20)+M20,"")</x:f>
+      </x:c>
+      <x:c r="O20" s="8" t="str">
+        <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
+      </x:c>
+      <x:c r="P20" s="8" t="str">
+        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+      </x:c>
+      <x:c r="Q20" s="9"/>
+      <x:c r="R20" s="9"/>
+      <x:c r="S20" s="13"/>
+      <x:c r="T20" s="9"/>
+      <x:c r="U20" s="9"/>
+      <x:c r="V20" s="9"/>
+      <x:c r="W20" s="9"/>
+      <x:c r="X20" s="9"/>
+      <x:c r="Y20" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+      <x:c r="Z20" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="Y7:Y13">
+  <x:conditionalFormatting sqref="Y7:Y20">
     <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:dataValidations count="3">
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="M7:M13">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="M7:M20">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="R7:R13">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="R7:R20">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="S7:S13">
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="S7:S20">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09c9c8e2a8de4c47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bf9ae71bcc9404b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2118,7 +2544,7 @@
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B7" s="8" t="n">
         <x:v>1</x:v>
@@ -2127,10 +2553,10 @@
         <x:v>48.895</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>1.85</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
-        <x:v>-0.55</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
         <x:f>0</x:f>
@@ -2142,7 +2568,7 @@
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
       <x:c r="A8" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B8" s="8" t="n">
         <x:v>2</x:v>
@@ -2151,10 +2577,10 @@
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>1.85</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>-0.55</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
         <x:f>SQRT((C8-C7)^2+(D8-D7)^2+(E8-E7)^2)</x:f>
@@ -2166,7 +2592,7 @@
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
       <x:c r="A9" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B9" s="8" t="n">
         <x:v>3</x:v>
@@ -2175,14 +2601,14 @@
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>1.85</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
         <x:f>SQRT((C9-C8)^2+(D9-D8)^2+(E9-E8)^2)</x:f>
-        <x:v>1.6900000000000002</x:v>
+        <x:v>0.6900000000000002</x:v>
       </x:c>
       <x:c r="G9" s="8" t="str">
         <x:v>Current</x:v>
@@ -2190,7 +2616,7 @@
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
       <x:c r="A10" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B10" s="8" t="n">
         <x:v>4</x:v>
@@ -2206,7 +2632,7 @@
       </x:c>
       <x:c r="F10" s="11" t="n">
         <x:f>SQRT((C10-C9)^2+(D10-D9)^2+(E10-E9)^2)</x:f>
-        <x:v>2.48</x:v>
+        <x:v>2.58</x:v>
       </x:c>
       <x:c r="G10" s="8" t="str">
         <x:v>Current</x:v>
@@ -2214,7 +2640,7 @@
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
       <x:c r="A11" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B11" s="8" t="n">
         <x:v>5</x:v>
@@ -2238,7 +2664,7 @@
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
       <x:c r="A12" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B12" s="8" t="n">
         <x:v>6</x:v>
@@ -2262,7 +2688,7 @@
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
       <x:c r="A13" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B13" s="8" t="n">
         <x:v>7</x:v>
@@ -2286,7 +2712,7 @@
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
       <x:c r="A14" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B14" s="8" t="n">
         <x:v>8</x:v>
@@ -2310,7 +2736,7 @@
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
       <x:c r="A15" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B15" s="8" t="n">
         <x:v>9</x:v>
@@ -2334,7 +2760,7 @@
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
       <x:c r="A16" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B16" s="8" t="n">
         <x:v>10</x:v>
@@ -2358,7 +2784,7 @@
     </x:row>
     <x:row r="17" ht="32" customHeight="1">
       <x:c r="A17" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B17" s="8" t="n">
         <x:v>11</x:v>
@@ -2382,7 +2808,7 @@
     </x:row>
     <x:row r="18" ht="32" customHeight="1">
       <x:c r="A18" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B18" s="8" t="n">
         <x:v>12</x:v>
@@ -2406,7 +2832,7 @@
     </x:row>
     <x:row r="19" ht="32" customHeight="1">
       <x:c r="A19" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B19" s="8" t="n">
         <x:v>13</x:v>
@@ -2430,7 +2856,7 @@
     </x:row>
     <x:row r="20" ht="32" customHeight="1">
       <x:c r="A20" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B20" s="8" t="n">
         <x:v>14</x:v>
@@ -2454,7 +2880,7 @@
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
       <x:c r="A21" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B21" s="8" t="n">
         <x:v>15</x:v>
@@ -2478,7 +2904,7 @@
     </x:row>
     <x:row r="22" ht="32" customHeight="1">
       <x:c r="A22" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B22" s="8" t="n">
         <x:v>16</x:v>
@@ -2502,7 +2928,7 @@
     </x:row>
     <x:row r="23" ht="32" customHeight="1">
       <x:c r="A23" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B23" s="8" t="n">
         <x:v>17</x:v>
@@ -2526,7 +2952,7 @@
     </x:row>
     <x:row r="24" ht="32" customHeight="1">
       <x:c r="A24" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B24" s="8" t="n">
         <x:v>18</x:v>
@@ -2550,7 +2976,7 @@
     </x:row>
     <x:row r="25" ht="32" customHeight="1">
       <x:c r="A25" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>trunk:DB1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B25" s="8" t="n">
         <x:v>19</x:v>
@@ -2574,7 +3000,7 @@
     </x:row>
     <x:row r="26" ht="32" customHeight="1">
       <x:c r="A26" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+        <x:v>drop:DB1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="B26" s="8" t="n">
         <x:v>1</x:v>
@@ -2598,7 +3024,7 @@
     </x:row>
     <x:row r="27" ht="32" customHeight="1">
       <x:c r="A27" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+        <x:v>drop:DB1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="B27" s="8" t="n">
         <x:v>2</x:v>
@@ -2622,7 +3048,7 @@
     </x:row>
     <x:row r="28" ht="32" customHeight="1">
       <x:c r="A28" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+        <x:v>drop:DB1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="B28" s="8" t="n">
         <x:v>3</x:v>
@@ -2646,7 +3072,7 @@
     </x:row>
     <x:row r="29" ht="32" customHeight="1">
       <x:c r="A29" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+        <x:v>drop:DB1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="B29" s="8" t="n">
         <x:v>4</x:v>
@@ -2670,7 +3096,7 @@
     </x:row>
     <x:row r="30" ht="32" customHeight="1">
       <x:c r="A30" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+        <x:v>drop:DB1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="B30" s="8" t="n">
         <x:v>5</x:v>
@@ -2694,7 +3120,7 @@
     </x:row>
     <x:row r="31" ht="32" customHeight="1">
       <x:c r="A31" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+        <x:v>drop:DB1:E1:light:-1:L156</x:v>
       </x:c>
       <x:c r="B31" s="8" t="n">
         <x:v>1</x:v>
@@ -2718,7 +3144,7 @@
     </x:row>
     <x:row r="32" ht="32" customHeight="1">
       <x:c r="A32" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+        <x:v>drop:DB1:E1:light:-1:L156</x:v>
       </x:c>
       <x:c r="B32" s="8" t="n">
         <x:v>2</x:v>
@@ -2742,7 +3168,7 @@
     </x:row>
     <x:row r="33" ht="32" customHeight="1">
       <x:c r="A33" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+        <x:v>drop:DB1:E1:light:-1:L156</x:v>
       </x:c>
       <x:c r="B33" s="8" t="n">
         <x:v>3</x:v>
@@ -2766,7 +3192,7 @@
     </x:row>
     <x:row r="34" ht="32" customHeight="1">
       <x:c r="A34" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L158</x:v>
+        <x:v>drop:DB1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B34" s="8" t="n">
         <x:v>1</x:v>
@@ -2790,7 +3216,7 @@
     </x:row>
     <x:row r="35" ht="32" customHeight="1">
       <x:c r="A35" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L158</x:v>
+        <x:v>drop:DB1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B35" s="8" t="n">
         <x:v>2</x:v>
@@ -2814,7 +3240,7 @@
     </x:row>
     <x:row r="36" ht="32" customHeight="1">
       <x:c r="A36" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L158</x:v>
+        <x:v>drop:DB1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B36" s="8" t="n">
         <x:v>3</x:v>
@@ -2838,7 +3264,7 @@
     </x:row>
     <x:row r="37" ht="32" customHeight="1">
       <x:c r="A37" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B37" s="8" t="n">
         <x:v>1</x:v>
@@ -2847,10 +3273,10 @@
         <x:v>48.895</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>1.85</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>-0.55</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
         <x:f>0</x:f>
@@ -2862,7 +3288,7 @@
     </x:row>
     <x:row r="38" ht="32" customHeight="1">
       <x:c r="A38" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B38" s="8" t="n">
         <x:v>2</x:v>
@@ -2871,10 +3297,10 @@
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>1.85</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>-0.55</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
         <x:f>SQRT((C38-C37)^2+(D38-D37)^2+(E38-E37)^2)</x:f>
@@ -2886,7 +3312,7 @@
     </x:row>
     <x:row r="39" ht="32" customHeight="1">
       <x:c r="A39" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B39" s="8" t="n">
         <x:v>3</x:v>
@@ -2895,14 +3321,14 @@
         <x:v>48.735</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>1.85</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
         <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
         <x:f>SQRT((C39-C38)^2+(D39-D38)^2+(E39-E38)^2)</x:f>
-        <x:v>1.6900000000000002</x:v>
+        <x:v>0.6900000000000002</x:v>
       </x:c>
       <x:c r="G39" s="8" t="str">
         <x:v>Current</x:v>
@@ -2910,7 +3336,7 @@
     </x:row>
     <x:row r="40" ht="32" customHeight="1">
       <x:c r="A40" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B40" s="8" t="n">
         <x:v>4</x:v>
@@ -2926,7 +3352,7 @@
       </x:c>
       <x:c r="F40" s="11" t="n">
         <x:f>SQRT((C40-C39)^2+(D40-D39)^2+(E40-E39)^2)</x:f>
-        <x:v>2.48</x:v>
+        <x:v>2.58</x:v>
       </x:c>
       <x:c r="G40" s="8" t="str">
         <x:v>Current</x:v>
@@ -2934,7 +3360,7 @@
     </x:row>
     <x:row r="41" ht="32" customHeight="1">
       <x:c r="A41" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B41" s="8" t="n">
         <x:v>5</x:v>
@@ -2958,7 +3384,7 @@
     </x:row>
     <x:row r="42" ht="32" customHeight="1">
       <x:c r="A42" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B42" s="8" t="n">
         <x:v>6</x:v>
@@ -2982,7 +3408,7 @@
     </x:row>
     <x:row r="43" ht="32" customHeight="1">
       <x:c r="A43" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B43" s="8" t="n">
         <x:v>7</x:v>
@@ -3006,7 +3432,7 @@
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
       <x:c r="A44" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B44" s="8" t="n">
         <x:v>8</x:v>
@@ -3030,7 +3456,7 @@
     </x:row>
     <x:row r="45" ht="32" customHeight="1">
       <x:c r="A45" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B45" s="8" t="n">
         <x:v>9</x:v>
@@ -3054,7 +3480,7 @@
     </x:row>
     <x:row r="46" ht="32" customHeight="1">
       <x:c r="A46" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B46" s="8" t="n">
         <x:v>10</x:v>
@@ -3078,7 +3504,7 @@
     </x:row>
     <x:row r="47" ht="32" customHeight="1">
       <x:c r="A47" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B47" s="8" t="n">
         <x:v>11</x:v>
@@ -3102,7 +3528,7 @@
     </x:row>
     <x:row r="48" ht="32" customHeight="1">
       <x:c r="A48" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B48" s="8" t="n">
         <x:v>12</x:v>
@@ -3126,7 +3552,7 @@
     </x:row>
     <x:row r="49" ht="32" customHeight="1">
       <x:c r="A49" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B49" s="8" t="n">
         <x:v>13</x:v>
@@ -3150,7 +3576,7 @@
     </x:row>
     <x:row r="50" ht="32" customHeight="1">
       <x:c r="A50" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B50" s="8" t="n">
         <x:v>14</x:v>
@@ -3174,7 +3600,7 @@
     </x:row>
     <x:row r="51" ht="32" customHeight="1">
       <x:c r="A51" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B51" s="8" t="n">
         <x:v>15</x:v>
@@ -3198,7 +3624,7 @@
     </x:row>
     <x:row r="52" ht="32" customHeight="1">
       <x:c r="A52" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B52" s="8" t="n">
         <x:v>16</x:v>
@@ -3222,7 +3648,7 @@
     </x:row>
     <x:row r="53" ht="32" customHeight="1">
       <x:c r="A53" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B53" s="8" t="n">
         <x:v>17</x:v>
@@ -3246,7 +3672,7 @@
     </x:row>
     <x:row r="54" ht="32" customHeight="1">
       <x:c r="A54" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B54" s="8" t="n">
         <x:v>18</x:v>
@@ -3270,7 +3696,7 @@
     </x:row>
     <x:row r="55" ht="32" customHeight="1">
       <x:c r="A55" s="8" t="str">
-        <x:v>drop:LC1:E1:light:1:L157</x:v>
+        <x:v>drop:DB1:E1:light:1:L157</x:v>
       </x:c>
       <x:c r="B55" s="8" t="n">
         <x:v>1</x:v>
@@ -3294,7 +3720,7 @@
     </x:row>
     <x:row r="56" ht="32" customHeight="1">
       <x:c r="A56" s="8" t="str">
-        <x:v>drop:LC1:E1:light:1:L157</x:v>
+        <x:v>drop:DB1:E1:light:1:L157</x:v>
       </x:c>
       <x:c r="B56" s="8" t="n">
         <x:v>2</x:v>
@@ -3318,7 +3744,7 @@
     </x:row>
     <x:row r="57" ht="32" customHeight="1">
       <x:c r="A57" s="8" t="str">
-        <x:v>drop:LC1:E1:light:1:L157</x:v>
+        <x:v>drop:DB1:E1:light:1:L157</x:v>
       </x:c>
       <x:c r="B57" s="8" t="n">
         <x:v>3</x:v>
@@ -3342,7 +3768,7 @@
     </x:row>
     <x:row r="58" ht="32" customHeight="1">
       <x:c r="A58" s="8" t="str">
-        <x:v>drop:LC1:E1:light:1:L159</x:v>
+        <x:v>drop:DB1:E1:light:1:L159</x:v>
       </x:c>
       <x:c r="B58" s="8" t="n">
         <x:v>1</x:v>
@@ -3366,7 +3792,7 @@
     </x:row>
     <x:row r="59" ht="32" customHeight="1">
       <x:c r="A59" s="8" t="str">
-        <x:v>drop:LC1:E1:light:1:L159</x:v>
+        <x:v>drop:DB1:E1:light:1:L159</x:v>
       </x:c>
       <x:c r="B59" s="8" t="n">
         <x:v>2</x:v>
@@ -3390,7 +3816,7 @@
     </x:row>
     <x:row r="60" ht="32" customHeight="1">
       <x:c r="A60" s="8" t="str">
-        <x:v>drop:LC1:E1:light:1:L159</x:v>
+        <x:v>drop:DB1:E1:light:1:L159</x:v>
       </x:c>
       <x:c r="B60" s="8" t="n">
         <x:v>3</x:v>
@@ -3412,13 +3838,1309 @@
         <x:v>Current</x:v>
       </x:c>
     </x:row>
+    <x:row r="61" ht="32" customHeight="1">
+      <x:c r="A61" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B61" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C61" s="11" t="n">
+        <x:v>48.895</x:v>
+      </x:c>
+      <x:c r="D61" s="11" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="E61" s="11" t="n">
+        <x:v>-0.55</x:v>
+      </x:c>
+      <x:c r="F61" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G61" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="32" customHeight="1">
+      <x:c r="A62" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B62" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C62" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D62" s="11" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="E62" s="11" t="n">
+        <x:v>-0.55</x:v>
+      </x:c>
+      <x:c r="F62" s="11" t="n">
+        <x:f>SQRT((C62-C61)^2+(D62-D61)^2+(E62-E61)^2)</x:f>
+        <x:v>0.1600000000000037</x:v>
+      </x:c>
+      <x:c r="G62" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="32" customHeight="1">
+      <x:c r="A63" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B63" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C63" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D63" s="11" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="E63" s="11" t="n">
+        <x:v>-2.24</x:v>
+      </x:c>
+      <x:c r="F63" s="11" t="n">
+        <x:f>SQRT((C63-C62)^2+(D63-D62)^2+(E63-E62)^2)</x:f>
+        <x:v>1.6900000000000002</x:v>
+      </x:c>
+      <x:c r="G63" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="32" customHeight="1">
+      <x:c r="A64" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B64" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C64" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D64" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E64" s="11" t="n">
+        <x:v>-2.24</x:v>
+      </x:c>
+      <x:c r="F64" s="11" t="n">
+        <x:f>SQRT((C64-C63)^2+(D64-D63)^2+(E64-E63)^2)</x:f>
+        <x:v>2.48</x:v>
+      </x:c>
+      <x:c r="G64" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="32" customHeight="1">
+      <x:c r="A65" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B65" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C65" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D65" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E65" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F65" s="11" t="n">
+        <x:f>SQRT((C65-C64)^2+(D65-D64)^2+(E65-E64)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
+      </x:c>
+      <x:c r="G65" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="32" customHeight="1">
+      <x:c r="A66" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B66" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C66" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D66" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E66" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F66" s="11" t="n">
+        <x:f>SQRT((C66-C65)^2+(D66-D65)^2+(E66-E65)^2)</x:f>
+        <x:v>4.280999999999999</x:v>
+      </x:c>
+      <x:c r="G66" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="32" customHeight="1">
+      <x:c r="A67" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B67" s="8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C67" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D67" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E67" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F67" s="11" t="n">
+        <x:f>SQRT((C67-C66)^2+(D67-D66)^2+(E67-E66)^2)</x:f>
+        <x:v>1.6580000000000004</x:v>
+      </x:c>
+      <x:c r="G67" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="32" customHeight="1">
+      <x:c r="A68" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B68" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C68" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D68" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E68" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F68" s="11" t="n">
+        <x:f>SQRT((C68-C67)^2+(D68-D67)^2+(E68-E67)^2)</x:f>
+        <x:v>4.0600000000000005</x:v>
+      </x:c>
+      <x:c r="G68" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="32" customHeight="1">
+      <x:c r="A69" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B69" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C69" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D69" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E69" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F69" s="11" t="n">
+        <x:f>SQRT((C69-C68)^2+(D69-D68)^2+(E69-E68)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
+      </x:c>
+      <x:c r="G69" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="32" customHeight="1">
+      <x:c r="A70" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B70" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C70" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D70" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E70" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F70" s="11" t="n">
+        <x:f>SQRT((C70-C69)^2+(D70-D69)^2+(E70-E69)^2)</x:f>
+        <x:v>1.0519999999999996</x:v>
+      </x:c>
+      <x:c r="G70" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="32" customHeight="1">
+      <x:c r="A71" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B71" s="8" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C71" s="11" t="n">
+        <x:v>43.535</x:v>
+      </x:c>
+      <x:c r="D71" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E71" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F71" s="11" t="n">
+        <x:f>SQRT((C71-C70)^2+(D71-D70)^2+(E71-E70)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G71" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="32" customHeight="1">
+      <x:c r="A72" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B72" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C72" s="11" t="n">
+        <x:v>43.455</x:v>
+      </x:c>
+      <x:c r="D72" s="11" t="n">
+        <x:v>6.950412371134024</x:v>
+      </x:c>
+      <x:c r="E72" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F72" s="11" t="n">
+        <x:f>SQRT((C72-C71)^2+(D72-D71)^2+(E72-E71)^2)</x:f>
+        <x:v>0.12010804821421249</x:v>
+      </x:c>
+      <x:c r="G72" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="32" customHeight="1">
+      <x:c r="A73" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B73" s="8" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C73" s="11" t="n">
+        <x:v>40.574999999999996</x:v>
+      </x:c>
+      <x:c r="D73" s="11" t="n">
+        <x:v>9.269999999999994</x:v>
+      </x:c>
+      <x:c r="E73" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F73" s="11" t="n">
+        <x:f>SQRT((C73-C72)^2+(D73-D72)^2+(E73-E72)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
+      </x:c>
+      <x:c r="G73" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="32" customHeight="1">
+      <x:c r="A74" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B74" s="8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C74" s="11" t="n">
+        <x:v>37.695</x:v>
+      </x:c>
+      <x:c r="D74" s="11" t="n">
+        <x:v>6.950412371134018</x:v>
+      </x:c>
+      <x:c r="E74" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F74" s="11" t="n">
+        <x:f>SQRT((C74-C73)^2+(D74-D73)^2+(E74-E73)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
+      </x:c>
+      <x:c r="G74" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="32" customHeight="1">
+      <x:c r="A75" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B75" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C75" s="11" t="n">
+        <x:v>37.615</x:v>
+      </x:c>
+      <x:c r="D75" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E75" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F75" s="11" t="n">
+        <x:f>SQRT((C75-C74)^2+(D75-D74)^2+(E75-E74)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
+      </x:c>
+      <x:c r="G75" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="32" customHeight="1">
+      <x:c r="A76" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B76" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C76" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D76" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E76" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F76" s="11" t="n">
+        <x:f>SQRT((C76-C75)^2+(D76-D75)^2+(E76-E75)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G76" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="32" customHeight="1">
+      <x:c r="A77" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B77" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C77" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D77" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E77" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F77" s="11" t="n">
+        <x:f>SQRT((C77-C76)^2+(D77-D76)^2+(E77-E76)^2)</x:f>
+        <x:v>1.0519999999999996</x:v>
+      </x:c>
+      <x:c r="G77" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="32" customHeight="1">
+      <x:c r="A78" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B78" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C78" s="11" t="n">
+        <x:v>5.475</x:v>
+      </x:c>
+      <x:c r="D78" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E78" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F78" s="11" t="n">
+        <x:f>SQRT((C78-C77)^2+(D78-D77)^2+(E78-E77)^2)</x:f>
+        <x:v>31.5</x:v>
+      </x:c>
+      <x:c r="G78" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="32" customHeight="1">
+      <x:c r="A79" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B79" s="8" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C79" s="11" t="n">
+        <x:v>2.65</x:v>
+      </x:c>
+      <x:c r="D79" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E79" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F79" s="11" t="n">
+        <x:f>SQRT((C79-C78)^2+(D79-D78)^2+(E79-E78)^2)</x:f>
+        <x:v>2.8249999999999997</x:v>
+      </x:c>
+      <x:c r="G79" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="32" customHeight="1">
+      <x:c r="A80" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+      </x:c>
+      <x:c r="B80" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C80" s="11" t="n">
+        <x:v>2.65</x:v>
+      </x:c>
+      <x:c r="D80" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E80" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F80" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G80" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="32" customHeight="1">
+      <x:c r="A81" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+      </x:c>
+      <x:c r="B81" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C81" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D81" s="11" t="n">
+        <x:v>7.65</x:v>
+      </x:c>
+      <x:c r="E81" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F81" s="11" t="n">
+        <x:f>SQRT((C81-C80)^2+(D81-D80)^2+(E81-E80)^2)</x:f>
+        <x:v>1.6888587862814344</x:v>
+      </x:c>
+      <x:c r="G81" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="32" customHeight="1">
+      <x:c r="A82" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+      </x:c>
+      <x:c r="B82" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C82" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D82" s="11" t="n">
+        <x:v>7.65</x:v>
+      </x:c>
+      <x:c r="E82" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F82" s="11" t="n">
+        <x:f>SQRT((C82-C81)^2+(D82-D81)^2+(E82-E81)^2)</x:f>
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="G82" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="32" customHeight="1">
+      <x:c r="A83" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+      </x:c>
+      <x:c r="B83" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C83" s="11" t="n">
+        <x:v>2.35</x:v>
+      </x:c>
+      <x:c r="D83" s="11" t="n">
+        <x:v>6.95</x:v>
+      </x:c>
+      <x:c r="E83" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F83" s="11" t="n">
+        <x:f>SQRT((C83-C82)^2+(D83-D82)^2+(E83-E82)^2)</x:f>
+        <x:v>0.7000000000000002</x:v>
+      </x:c>
+      <x:c r="G83" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="32" customHeight="1">
+      <x:c r="A84" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L155</x:v>
+      </x:c>
+      <x:c r="B84" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C84" s="11" t="n">
+        <x:v>2.65</x:v>
+      </x:c>
+      <x:c r="D84" s="11" t="n">
+        <x:v>6.95</x:v>
+      </x:c>
+      <x:c r="E84" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F84" s="11" t="n">
+        <x:f>SQRT((C84-C83)^2+(D84-D83)^2+(E84-E83)^2)</x:f>
+        <x:v>0.2999999999999998</x:v>
+      </x:c>
+      <x:c r="G84" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="32" customHeight="1">
+      <x:c r="A85" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+      </x:c>
+      <x:c r="B85" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C85" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D85" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E85" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F85" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G85" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="32" customHeight="1">
+      <x:c r="A86" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+      </x:c>
+      <x:c r="B86" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C86" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D86" s="11" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="E86" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F86" s="11" t="n">
+        <x:f>SQRT((C86-C85)^2+(D86-D85)^2+(E86-E85)^2)</x:f>
+        <x:v>1.3880000000000008</x:v>
+      </x:c>
+      <x:c r="G86" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="32" customHeight="1">
+      <x:c r="A87" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L156</x:v>
+      </x:c>
+      <x:c r="B87" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C87" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D87" s="11" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="E87" s="11" t="n">
+        <x:v>-7.245</x:v>
+      </x:c>
+      <x:c r="F87" s="11" t="n">
+        <x:f>SQRT((C87-C86)^2+(D87-D86)^2+(E87-E86)^2)</x:f>
+        <x:v>0.11500000000000021</x:v>
+      </x:c>
+      <x:c r="G87" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="32" customHeight="1">
+      <x:c r="A88" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L158</x:v>
+      </x:c>
+      <x:c r="B88" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C88" s="11" t="n">
+        <x:v>34.725</x:v>
+      </x:c>
+      <x:c r="D88" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E88" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F88" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G88" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="32" customHeight="1">
+      <x:c r="A89" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L158</x:v>
+      </x:c>
+      <x:c r="B89" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C89" s="11" t="n">
+        <x:v>34.725</x:v>
+      </x:c>
+      <x:c r="D89" s="11" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="E89" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F89" s="11" t="n">
+        <x:f>SQRT((C89-C88)^2+(D89-D88)^2+(E89-E88)^2)</x:f>
+        <x:v>1.3880000000000008</x:v>
+      </x:c>
+      <x:c r="G89" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="32" customHeight="1">
+      <x:c r="A90" s="8" t="str">
+        <x:v>drop:LC1:E1:light:-1:L158</x:v>
+      </x:c>
+      <x:c r="B90" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C90" s="11" t="n">
+        <x:v>34.725</x:v>
+      </x:c>
+      <x:c r="D90" s="11" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="E90" s="11" t="n">
+        <x:v>-7.245</x:v>
+      </x:c>
+      <x:c r="F90" s="11" t="n">
+        <x:f>SQRT((C90-C89)^2+(D90-D89)^2+(E90-E89)^2)</x:f>
+        <x:v>0.11500000000000021</x:v>
+      </x:c>
+      <x:c r="G90" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="32" customHeight="1">
+      <x:c r="A91" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B91" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C91" s="11" t="n">
+        <x:v>48.895</x:v>
+      </x:c>
+      <x:c r="D91" s="11" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="E91" s="11" t="n">
+        <x:v>-0.55</x:v>
+      </x:c>
+      <x:c r="F91" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G91" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="32" customHeight="1">
+      <x:c r="A92" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B92" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C92" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D92" s="11" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="E92" s="11" t="n">
+        <x:v>-0.55</x:v>
+      </x:c>
+      <x:c r="F92" s="11" t="n">
+        <x:f>SQRT((C92-C91)^2+(D92-D91)^2+(E92-E91)^2)</x:f>
+        <x:v>0.1600000000000037</x:v>
+      </x:c>
+      <x:c r="G92" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="32" customHeight="1">
+      <x:c r="A93" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B93" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C93" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D93" s="11" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="E93" s="11" t="n">
+        <x:v>-2.24</x:v>
+      </x:c>
+      <x:c r="F93" s="11" t="n">
+        <x:f>SQRT((C93-C92)^2+(D93-D92)^2+(E93-E92)^2)</x:f>
+        <x:v>1.6900000000000002</x:v>
+      </x:c>
+      <x:c r="G93" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="32" customHeight="1">
+      <x:c r="A94" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B94" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C94" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D94" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E94" s="11" t="n">
+        <x:v>-2.24</x:v>
+      </x:c>
+      <x:c r="F94" s="11" t="n">
+        <x:f>SQRT((C94-C93)^2+(D94-D93)^2+(E94-E93)^2)</x:f>
+        <x:v>2.48</x:v>
+      </x:c>
+      <x:c r="G94" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="32" customHeight="1">
+      <x:c r="A95" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B95" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C95" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D95" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E95" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F95" s="11" t="n">
+        <x:f>SQRT((C95-C94)^2+(D95-D94)^2+(E95-E94)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
+      </x:c>
+      <x:c r="G95" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="32" customHeight="1">
+      <x:c r="A96" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B96" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C96" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D96" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E96" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F96" s="11" t="n">
+        <x:f>SQRT((C96-C95)^2+(D96-D95)^2+(E96-E95)^2)</x:f>
+        <x:v>4.280999999999999</x:v>
+      </x:c>
+      <x:c r="G96" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="32" customHeight="1">
+      <x:c r="A97" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B97" s="8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C97" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D97" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E97" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F97" s="11" t="n">
+        <x:f>SQRT((C97-C96)^2+(D97-D96)^2+(E97-E96)^2)</x:f>
+        <x:v>1.6580000000000004</x:v>
+      </x:c>
+      <x:c r="G97" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="32" customHeight="1">
+      <x:c r="A98" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B98" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C98" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D98" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E98" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F98" s="11" t="n">
+        <x:f>SQRT((C98-C97)^2+(D98-D97)^2+(E98-E97)^2)</x:f>
+        <x:v>10.66</x:v>
+      </x:c>
+      <x:c r="G98" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="32" customHeight="1">
+      <x:c r="A99" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B99" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C99" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D99" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E99" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F99" s="11" t="n">
+        <x:f>SQRT((C99-C98)^2+(D99-D98)^2+(E99-E98)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
+      </x:c>
+      <x:c r="G99" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="32" customHeight="1">
+      <x:c r="A100" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B100" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C100" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D100" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E100" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F100" s="11" t="n">
+        <x:f>SQRT((C100-C99)^2+(D100-D99)^2+(E100-E99)^2)</x:f>
+        <x:v>1.0519999999999996</x:v>
+      </x:c>
+      <x:c r="G100" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="32" customHeight="1">
+      <x:c r="A101" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B101" s="8" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C101" s="11" t="n">
+        <x:v>43.535</x:v>
+      </x:c>
+      <x:c r="D101" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E101" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F101" s="11" t="n">
+        <x:f>SQRT((C101-C100)^2+(D101-D100)^2+(E101-E100)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G101" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="32" customHeight="1">
+      <x:c r="A102" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B102" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C102" s="11" t="n">
+        <x:v>43.455</x:v>
+      </x:c>
+      <x:c r="D102" s="11" t="n">
+        <x:v>6.950412371134024</x:v>
+      </x:c>
+      <x:c r="E102" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F102" s="11" t="n">
+        <x:f>SQRT((C102-C101)^2+(D102-D101)^2+(E102-E101)^2)</x:f>
+        <x:v>0.12010804821421249</x:v>
+      </x:c>
+      <x:c r="G102" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="32" customHeight="1">
+      <x:c r="A103" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B103" s="8" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C103" s="11" t="n">
+        <x:v>40.574999999999996</x:v>
+      </x:c>
+      <x:c r="D103" s="11" t="n">
+        <x:v>9.269999999999994</x:v>
+      </x:c>
+      <x:c r="E103" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F103" s="11" t="n">
+        <x:f>SQRT((C103-C102)^2+(D103-D102)^2+(E103-E102)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
+      </x:c>
+      <x:c r="G103" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="32" customHeight="1">
+      <x:c r="A104" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B104" s="8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C104" s="11" t="n">
+        <x:v>37.695</x:v>
+      </x:c>
+      <x:c r="D104" s="11" t="n">
+        <x:v>6.950412371134018</x:v>
+      </x:c>
+      <x:c r="E104" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F104" s="11" t="n">
+        <x:f>SQRT((C104-C103)^2+(D104-D103)^2+(E104-E103)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
+      </x:c>
+      <x:c r="G104" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="32" customHeight="1">
+      <x:c r="A105" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B105" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C105" s="11" t="n">
+        <x:v>37.615</x:v>
+      </x:c>
+      <x:c r="D105" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E105" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F105" s="11" t="n">
+        <x:f>SQRT((C105-C104)^2+(D105-D104)^2+(E105-E104)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
+      </x:c>
+      <x:c r="G105" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="32" customHeight="1">
+      <x:c r="A106" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B106" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C106" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D106" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E106" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F106" s="11" t="n">
+        <x:f>SQRT((C106-C105)^2+(D106-D105)^2+(E106-E105)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G106" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="32" customHeight="1">
+      <x:c r="A107" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B107" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C107" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D107" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E107" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F107" s="11" t="n">
+        <x:f>SQRT((C107-C106)^2+(D107-D106)^2+(E107-E106)^2)</x:f>
+        <x:v>1.0519999999999996</x:v>
+      </x:c>
+      <x:c r="G107" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="32" customHeight="1">
+      <x:c r="A108" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B108" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C108" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D108" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E108" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F108" s="11" t="n">
+        <x:f>SQRT((C108-C107)^2+(D108-D107)^2+(E108-E107)^2)</x:f>
+        <x:v>20.25</x:v>
+      </x:c>
+      <x:c r="G108" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="32" customHeight="1">
+      <x:c r="A109" s="8" t="str">
+        <x:v>drop:LC1:E1:light:1:L157</x:v>
+      </x:c>
+      <x:c r="B109" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C109" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D109" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E109" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F109" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G109" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="32" customHeight="1">
+      <x:c r="A110" s="8" t="str">
+        <x:v>drop:LC1:E1:light:1:L157</x:v>
+      </x:c>
+      <x:c r="B110" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C110" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D110" s="11" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="E110" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F110" s="11" t="n">
+        <x:f>SQRT((C110-C109)^2+(D110-D109)^2+(E110-E109)^2)</x:f>
+        <x:v>1.3880000000000008</x:v>
+      </x:c>
+      <x:c r="G110" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="32" customHeight="1">
+      <x:c r="A111" s="8" t="str">
+        <x:v>drop:LC1:E1:light:1:L157</x:v>
+      </x:c>
+      <x:c r="B111" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C111" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D111" s="11" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="E111" s="11" t="n">
+        <x:v>7.245</x:v>
+      </x:c>
+      <x:c r="F111" s="11" t="n">
+        <x:f>SQRT((C111-C110)^2+(D111-D110)^2+(E111-E110)^2)</x:f>
+        <x:v>0.11500000000000021</x:v>
+      </x:c>
+      <x:c r="G111" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="32" customHeight="1">
+      <x:c r="A112" s="8" t="str">
+        <x:v>drop:LC1:E1:light:1:L159</x:v>
+      </x:c>
+      <x:c r="B112" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C112" s="11" t="n">
+        <x:v>34.725</x:v>
+      </x:c>
+      <x:c r="D112" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E112" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F112" s="11" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G112" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="32" customHeight="1">
+      <x:c r="A113" s="8" t="str">
+        <x:v>drop:LC1:E1:light:1:L159</x:v>
+      </x:c>
+      <x:c r="B113" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C113" s="11" t="n">
+        <x:v>34.725</x:v>
+      </x:c>
+      <x:c r="D113" s="11" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="E113" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F113" s="11" t="n">
+        <x:f>SQRT((C113-C112)^2+(D113-D112)^2+(E113-E112)^2)</x:f>
+        <x:v>1.3880000000000008</x:v>
+      </x:c>
+      <x:c r="G113" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="32" customHeight="1">
+      <x:c r="A114" s="8" t="str">
+        <x:v>drop:LC1:E1:light:1:L159</x:v>
+      </x:c>
+      <x:c r="B114" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C114" s="11" t="n">
+        <x:v>34.725</x:v>
+      </x:c>
+      <x:c r="D114" s="11" t="n">
+        <x:v>4.6</x:v>
+      </x:c>
+      <x:c r="E114" s="11" t="n">
+        <x:v>7.245</x:v>
+      </x:c>
+      <x:c r="F114" s="11" t="n">
+        <x:f>SQRT((C114-C113)^2+(D114-D113)^2+(E114-E113)^2)</x:f>
+        <x:v>0.11500000000000021</x:v>
+      </x:c>
+      <x:c r="G114" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G7:G60">
+  <x:conditionalFormatting sqref="G7:G114">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31c53e96d2b54268"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6baea678b7fd440e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4141ac97736d4bc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R890ebeb3bdac4472"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rb1262e2df6094241"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra6432967daba49bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Read8a41f1238464c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R71f27fe6bd3746e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc381628d8a8a4337"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R6bb02b820b1e4653"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,7 +487,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-09T04:54:03.663Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-09T06:49:14.923Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +570,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>e8b0d45e0c5518ca0cc64c1fa511adc8ba03ba31bef6d46426ff3c0c3e699bab</x:v>
+        <x:v>0a6cf2aa5294b46ad1ca267ef78dada74d793fdb4a83f39e392746594b74ba7c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -1314,7 +1314,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63d13117f67b4d03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77e5867e232a48c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2448,7 +2448,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bf9ae71bcc9404b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b5e3fa13e0d481a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5140,7 +5140,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6baea678b7fd440e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1692e5e513f64cee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Read8a41f1238464c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R71f27fe6bd3746e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc381628d8a8a4337"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R6bb02b820b1e4653"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4a4dbae8464346e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R233adc532c654bcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R97a4193a13f34a37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R72d8a0f1da4b476d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -77,7 +77,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -487,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-09T06:49:14.923Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-17T21:08:50.163Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -570,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>0a6cf2aa5294b46ad1ca267ef78dada74d793fdb4a83f39e392746594b74ba7c</x:v>
+        <x:v>37e3acfbe7b2353ccb6bf951d166ae573b85d990a0e3cb06b573b995c64fefa8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -578,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e25c59374b1948a67cdb0ee5bed0beb9884da65931cb92b8dc2af738d4ae1e28</x:v>
+        <x:v>dbabc0c9ddcd7207edad13de9e8b20f5da0865700167c5f9fe7c34d6d03b22b4</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1314,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77e5867e232a48c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02ad3c5677134257"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2448,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b5e3fa13e0d481a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54dc7f490b63480a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5140,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1692e5e513f64cee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4353b6c0712f4f66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R4a4dbae8464346e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R233adc532c654bcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R97a4193a13f34a37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R72d8a0f1da4b476d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rfd5e0c22c503492a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rc0d210a507b042e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc1fa4b7b2f674609"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc548fe34c5e544cd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-17T21:08:50.163Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-17T21:33:54.811Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>37e3acfbe7b2353ccb6bf951d166ae573b85d990a0e3cb06b573b995c64fefa8</x:v>
+        <x:v>40c0fb48adb616822d2737a378024e64d46f211fcc43ca75ea298cd2570965f8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>dbabc0c9ddcd7207edad13de9e8b20f5da0865700167c5f9fe7c34d6d03b22b4</x:v>
+        <x:v>e8507810679907dc3354f9387ce0b6d5f3b3e307d5939a52680f19a914a4cd86</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02ad3c5677134257"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R389c681d51c14a24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54dc7f490b63480a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red8a2c0fc50d47fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4353b6c0712f4f66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R220b1346adce40fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rfd5e0c22c503492a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rc0d210a507b042e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc1fa4b7b2f674609"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc548fe34c5e544cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3f519f51c0114ade"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf799946d7f434ae4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R9fb10b0c08534188"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc3abf615cc8f4353"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-17T21:33:54.811Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-19T08:15:40.780Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>40c0fb48adb616822d2737a378024e64d46f211fcc43ca75ea298cd2570965f8</x:v>
+        <x:v>377a9614312a02f792043db75f19539177eac31dbb6fbce22ffc70cc36f6d6f9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>e8507810679907dc3354f9387ce0b6d5f3b3e307d5939a52680f19a914a4cd86</x:v>
+        <x:v>7407c92e37c8f0d1299afa3b00360d1b00fbe1db0f067d0666f57047093f1960</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R389c681d51c14a24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R288e7122068142cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red8a2c0fc50d47fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bbf800ffcfc4c38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R220b1346adce40fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f64ef56434a40c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3f519f51c0114ade"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf799946d7f434ae4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R9fb10b0c08534188"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc3abf615cc8f4353"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R8795dbd6f5854355"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Reefde54f651d4690"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R77502686a691439f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Raf220f51140442b7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-19T08:15:40.780Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-19T08:50:48.752Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>377a9614312a02f792043db75f19539177eac31dbb6fbce22ffc70cc36f6d6f9</x:v>
+        <x:v>5f987e29647ab0b5cedad770eae700cb80b204e95ea85d8a400edb95c4d1128d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R288e7122068142cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R112bf0b064134a51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bbf800ffcfc4c38"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc912bd1b4a384424"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f64ef56434a40c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56073d6804a346b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R8795dbd6f5854355"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Reefde54f651d4690"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R77502686a691439f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Raf220f51140442b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R64cdf51d36be4d81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9078d8b5e0ad4691"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R076cdb37d49b44f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R97f075411a0349d5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-19T08:50:48.752Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-19T11:17:33.830Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5f987e29647ab0b5cedad770eae700cb80b204e95ea85d8a400edb95c4d1128d</x:v>
+        <x:v>76909d79225afb700a61e3530abc09d363cc6e053b648e6ff87757a6c3bc33f9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>7407c92e37c8f0d1299afa3b00360d1b00fbe1db0f067d0666f57047093f1960</x:v>
+        <x:v>5c2b7909fdbf3eab73054e0a16a6cfe55decd4f3c81b9a88867863ffd7c0fef1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R112bf0b064134a51"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32f5434dbd7b4a5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc912bd1b4a384424"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75b85db679a04981"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56073d6804a346b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde325a81484e4ebd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R64cdf51d36be4d81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R9078d8b5e0ad4691"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R076cdb37d49b44f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R97f075411a0349d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9e777e4dd4e24c5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R0e7401fc83e64c92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rd2ab789c116643f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb9aff5bb3563423c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-19T11:17:33.830Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-19T13:14:34.808Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>76909d79225afb700a61e3530abc09d363cc6e053b648e6ff87757a6c3bc33f9</x:v>
+        <x:v>5e78147eff2f4a61ae97936ba8b51920b75ba77bd982e40a1cae0206f908332c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>5c2b7909fdbf3eab73054e0a16a6cfe55decd4f3c81b9a88867863ffd7c0fef1</x:v>
+        <x:v>7a659950a4bf89cc57551f6d9714dbafa89ad76ea9820ddefb4bbc73056b5b2e</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32f5434dbd7b4a5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0bf9b8b469140b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75b85db679a04981"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0aa924e260b343f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde325a81484e4ebd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3829b6c3b4aa4b0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9e777e4dd4e24c5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R0e7401fc83e64c92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rd2ab789c116643f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb9aff5bb3563423c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3528a4a769b6466d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R03dfe0262c784687"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R88b3a26ef0d4452e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rfb6562d6fa854548"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-19T13:14:34.808Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-23T23:29:38.571Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5e78147eff2f4a61ae97936ba8b51920b75ba77bd982e40a1cae0206f908332c</x:v>
+        <x:v>19eb3af4e9e190d44f45651a83746b308f3bc351650fff669ae77f5ce0cb3e9d</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>7a659950a4bf89cc57551f6d9714dbafa89ad76ea9820ddefb4bbc73056b5b2e</x:v>
+        <x:v>ec7eed586921cecf1c820f16f5ebefd971b44f66cd4eae78e00a7540b47ad9d9</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0bf9b8b469140b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R469e29d39b454f75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0aa924e260b343f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radcb34c0ca7e4f71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3829b6c3b4aa4b0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R153e53074b6246cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3528a4a769b6466d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R03dfe0262c784687"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R88b3a26ef0d4452e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rfb6562d6fa854548"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R05b979a9091c4e3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re4a09e4047dd461a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra2f13e3847464117"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra52e7f057e854fdc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-23T23:29:38.571Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T00:39:01.684Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>19eb3af4e9e190d44f45651a83746b308f3bc351650fff669ae77f5ce0cb3e9d</x:v>
+        <x:v>146da28a773b5232adb7a991941b4c52312ffa1c721c3656a3930b7eeac1bb23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>ec7eed586921cecf1c820f16f5ebefd971b44f66cd4eae78e00a7540b47ad9d9</x:v>
+        <x:v>c2461516b6454aa96dec6678dad1bc8b977620d5c08160037ef8b86f7f230532</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R469e29d39b454f75"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3f48b6f379a460c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radcb34c0ca7e4f71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96ef63e0cf634e91"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R153e53074b6246cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra14e71dd2db2490a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R05b979a9091c4e3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re4a09e4047dd461a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra2f13e3847464117"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Ra52e7f057e854fdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9237865312474438"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rddfd7ab031f6486e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6c73e4466a6a44f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R2212c29f06754786"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T00:39:01.684Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T16:03:51.012Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>146da28a773b5232adb7a991941b4c52312ffa1c721c3656a3930b7eeac1bb23</x:v>
+        <x:v>5426ce45cb04f814d5dd0210f8e96b572936a920fad8790c50d7c5cfa6b6676e</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>c2461516b6454aa96dec6678dad1bc8b977620d5c08160037ef8b86f7f230532</x:v>
+        <x:v>b17314130617491f3e73a772bab5720c8ffe36baa24ed5a5cc2512f8640338ef</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3f48b6f379a460c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c8a4b04af784147"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96ef63e0cf634e91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d699461e6cf43ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra14e71dd2db2490a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd58fd59ffcc488b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9237865312474438"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rddfd7ab031f6486e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6c73e4466a6a44f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R2212c29f06754786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Raa2248fa7e394c3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf9e27b154d4e4837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc82102f7adc84d56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R6ef6fa1292154b42"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T16:03:51.012Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T16:44:17.712Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5426ce45cb04f814d5dd0210f8e96b572936a920fad8790c50d7c5cfa6b6676e</x:v>
+        <x:v>c5d56493e89032b01436ecaed120866a09d5872d997065e2e10f3c09d0d21e41</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>b17314130617491f3e73a772bab5720c8ffe36baa24ed5a5cc2512f8640338ef</x:v>
+        <x:v>10d6d18e117107f62a3d3e48f08d9f8d9df9954b8ce3c3d85d06553452833a75</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c8a4b04af784147"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f2a7eb90ca04e75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d699461e6cf43ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95b82ecf4bbe4eaa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd58fd59ffcc488b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe245fcfaeb34db6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Raa2248fa7e394c3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rf9e27b154d4e4837"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rc82102f7adc84d56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R6ef6fa1292154b42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R2e311f3f33a64e90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rbbfa106ba8984837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rfeaffe779e77421e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R4b64cc04ff504026"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T16:44:17.712Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T17:01:56.972Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>c5d56493e89032b01436ecaed120866a09d5872d997065e2e10f3c09d0d21e41</x:v>
+        <x:v>13047932f1698050c4ec862686991828799970abdcdf394a64d82404d1fcbee8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>10d6d18e117107f62a3d3e48f08d9f8d9df9954b8ce3c3d85d06553452833a75</x:v>
+        <x:v>2faac8500a07543b677dc990e5aad2b96fa69acb639f440c57dab2001fa28053</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f2a7eb90ca04e75"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ea02aae174c4e69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95b82ecf4bbe4eaa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2be760e4367849ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe245fcfaeb34db6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e36e15150414d0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R2e311f3f33a64e90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rbbfa106ba8984837"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rfeaffe779e77421e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R4b64cc04ff504026"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R666b8d498ad049e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rad095ec0e91a43c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R992bbe0447b448b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1c7fb49cdd1f4ef7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T17:01:56.972Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T17:09:33.226Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>13047932f1698050c4ec862686991828799970abdcdf394a64d82404d1fcbee8</x:v>
+        <x:v>8494709266c989cc26ec0f16481a494804ce05b0210fea7ddf78e6004c0e1614</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>2faac8500a07543b677dc990e5aad2b96fa69acb639f440c57dab2001fa28053</x:v>
+        <x:v>760fbab99b5e7a6f8a94c497e4a9254bf06be7fb81bd104e0e2b4126c9fde701</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ea02aae174c4e69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec67b21eeb5e4e11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2be760e4367849ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67ca7f3eb9194c2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e36e15150414d0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c5c21258da9475b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R666b8d498ad049e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rad095ec0e91a43c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R992bbe0447b448b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R1c7fb49cdd1f4ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd2a4bcc4b42144f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R88bd2d304e7c4688"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Re13325fe28d44e8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R49339d0f292f4089"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T17:09:33.226Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T17:42:22.582Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>8494709266c989cc26ec0f16481a494804ce05b0210fea7ddf78e6004c0e1614</x:v>
+        <x:v>94f37cc477b452b68afd0631937580a0b9412b859965e9046c49f59c64746a3f</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>760fbab99b5e7a6f8a94c497e4a9254bf06be7fb81bd104e0e2b4126c9fde701</x:v>
+        <x:v>1c162288ea3d9215a1f3a3feb59b009079a72c6a8a777f9f9044923d3b18ad31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec67b21eeb5e4e11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38ee5ef92b4e4de6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67ca7f3eb9194c2f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0d71cd416064f82"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c5c21258da9475b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20a2668bf9c14200"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd2a4bcc4b42144f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R88bd2d304e7c4688"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Re13325fe28d44e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R49339d0f292f4089"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9e6387dd26c2483e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R146587aef8284a74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rda090ae504ca4e45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3f2ee489a11a465e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T17:42:22.582Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T17:49:59.196Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>94f37cc477b452b68afd0631937580a0b9412b859965e9046c49f59c64746a3f</x:v>
+        <x:v>88062f7a6e23d78621ee2f69e0c94047babf12437db78098dd47d3bedd6e18e8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>1c162288ea3d9215a1f3a3feb59b009079a72c6a8a777f9f9044923d3b18ad31</x:v>
+        <x:v>fb798ccf47bd62d17275121a5ca1021b3ed9a80358d236bd57d75a7be070b894</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38ee5ef92b4e4de6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf29d2f0c3104d4b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0d71cd416064f82"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb47561ade895403e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20a2668bf9c14200"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45cd4498aa264d80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R9e6387dd26c2483e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R146587aef8284a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rda090ae504ca4e45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3f2ee489a11a465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3a05aff551ac48f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rfd9f238d51534410"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra446faffc3d1420c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R2d1410169cdb4569"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T17:49:59.196Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T18:07:55.978Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>88062f7a6e23d78621ee2f69e0c94047babf12437db78098dd47d3bedd6e18e8</x:v>
+        <x:v>5385d4f4cf361a2e56db9b88d4a9952e6d93bf5f83f0834cb083bcdd6684e517</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>fb798ccf47bd62d17275121a5ca1021b3ed9a80358d236bd57d75a7be070b894</x:v>
+        <x:v>d50c68edff009ac84589ad37b15985dac299e304fb4daa2752ebe808d92740fd</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf29d2f0c3104d4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc58751194fd241e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb47561ade895403e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c166eb6d6774cfe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45cd4498aa264d80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba702c0afab440c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3a05aff551ac48f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Rfd9f238d51534410"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Ra446faffc3d1420c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R2d1410169cdb4569"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R094a62eed91f4774"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R7584e7191b9b4244"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R1145b8ed9215419f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R6fabbdf9a0d04694"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T18:07:55.978Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T18:15:14.532Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>5385d4f4cf361a2e56db9b88d4a9952e6d93bf5f83f0834cb083bcdd6684e517</x:v>
+        <x:v>944ecbe81a903e81a65ffa487f20c3a417603b0749843148bbf77414d42d60b4</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc58751194fd241e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R361469f2246d4c51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c166eb6d6774cfe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1977eb4ce3e4603"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba702c0afab440c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbda2529a6554a9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R094a62eed91f4774"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R7584e7191b9b4244"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R1145b8ed9215419f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R6fabbdf9a0d04694"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Ra13355ee5e164c9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1ea5384ecf064749"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R404221880ea04de8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R6ff15da9644248f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T18:15:14.532Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T22:22:25.930Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>944ecbe81a903e81a65ffa487f20c3a417603b0749843148bbf77414d42d60b4</x:v>
+        <x:v>325f8ef8696abef155a85a11a511a71ee5bbd155d28b2e0bfd11928b39ade4e3</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>d50c68edff009ac84589ad37b15985dac299e304fb4daa2752ebe808d92740fd</x:v>
+        <x:v>75fa53533f9758516132ea54608152663cd0f407a24b0e6a3e030bc743a6ab27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R361469f2246d4c51"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62d95505e8eb425e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1977eb4ce3e4603"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reeca7ec9a45441c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbda2529a6554a9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa91215ed0ae455c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Ra13355ee5e164c9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R1ea5384ecf064749"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R404221880ea04de8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R6ff15da9644248f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R51f6836ce5e94033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R251459aa016d4fce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R397f560833524946"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rd7b7ed0c845d4985"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-24T22:22:25.930Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-25T11:43:35.202Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>325f8ef8696abef155a85a11a511a71ee5bbd155d28b2e0bfd11928b39ade4e3</x:v>
+        <x:v>8794d15eced755667fbb94a78904d0b24ab39e7c75d28fc3bbe150bece4e8ceb</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>75fa53533f9758516132ea54608152663cd0f407a24b0e6a3e030bc743a6ab27</x:v>
+        <x:v>fa54e193a88aab1a463c7e9a9d929aac8295554193f697131ae924624c8c3635</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62d95505e8eb425e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99f6aec491764623"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reeca7ec9a45441c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5faa4abc567940b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5146,7 +5146,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa91215ed0ae455c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad2531560a5b4e59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R51f6836ce5e94033"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R251459aa016d4fce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R397f560833524946"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rd7b7ed0c845d4985"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R309fbb352740486f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R560c49c973d24ae4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rd3e8b4c22b9f4b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3ca4afe8b0da44e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -257,7 +257,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G114" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RouteVertexRegister" displayName="RouteVertexRegister" ref="A6:G128" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Route ID"/>
     <x:tableColumn id="2" name="Vertex"/>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-25T11:43:35.202Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-25T12:31:42.928Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>8794d15eced755667fbb94a78904d0b24ab39e7c75d28fc3bbe150bece4e8ceb</x:v>
+        <x:v>6638c6d858c0c15d03f1b8c7f8d4371e61b16cbc58edb9c36dd4e72b917f5303</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>fa54e193a88aab1a463c7e9a9d929aac8295554193f697131ae924624c8c3635</x:v>
+        <x:v>8efd0e5d2f1745401819248f5cd349c1ca2995df2b2938bff0ddd27c9679b4c8</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -972,10 +972,10 @@
         <x:v>E1</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>2.65</x:v>
+        <x:v>2.6800000008940703</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>6.95</x:v>
+        <x:v>4.762499999552966</x:v>
       </x:c>
       <x:c r="H7" s="11" t="n">
         <x:v>0</x:v>
@@ -1021,7 +1021,7 @@
         <x:v>drop:DB1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="AC7" s="8" t="str">
-        <x:v>{"dim":1}</x:v>
+        <x:v>{"backReach":0.08,"clipRise":0.1375000004470346,"dim":1,"note":"CONCEPT: inside-face transom clip, case below the coloured fanlight. Lowest edge about 4.68 m; support/door clearance and sign visibility need fire/architectural review. E1 remains maintained from DB-"}</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="96" customHeight="1">
@@ -1044,10 +1044,10 @@
         <x:v>16.725</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>4.6</x:v>
+        <x:v>3.061</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>-7.245</x:v>
+        <x:v>-7.4400000013411045</x:v>
       </x:c>
       <x:c r="I8" s="8" t="str">
         <x:v>wall</x:v>
@@ -1090,7 +1090,7 @@
         <x:v>drop:DB1:E1:light:-1:L156</x:v>
       </x:c>
       <x:c r="AC8" s="8" t="str">
-        <x:v>{"dim":1}</x:v>
+        <x:v>{"backReach":0,"clipRise":0,"dim":1,"note":"CONCEPT: mounted on the 220 mm fixed head band above the door leaves and below the coloured fanlight. E1 remains maintained from DB-1. Product, fixing, visibility and emergency operation require revie"}</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="96" customHeight="1">
@@ -1113,10 +1113,10 @@
         <x:v>16.725</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>4.6</x:v>
+        <x:v>3.061</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>7.245</x:v>
+        <x:v>7.4400000013411045</x:v>
       </x:c>
       <x:c r="I9" s="8" t="str">
         <x:v>wall</x:v>
@@ -1159,7 +1159,7 @@
         <x:v>drop:DB1:E1:light:1:L157</x:v>
       </x:c>
       <x:c r="AC9" s="8" t="str">
-        <x:v>{"dim":1}</x:v>
+        <x:v>{"backReach":0,"clipRise":0,"dim":1,"note":"CONCEPT: mounted on the 220 mm fixed head band above the door leaves and below the coloured fanlight. E1 remains maintained from DB-1. Product, fixing, visibility and emergency operation require revie"}</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="96" customHeight="1">
@@ -1182,10 +1182,10 @@
         <x:v>34.725</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>4.6</x:v>
+        <x:v>3.061</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
-        <x:v>-7.245</x:v>
+        <x:v>-7.4400000013411045</x:v>
       </x:c>
       <x:c r="I10" s="8" t="str">
         <x:v>wall</x:v>
@@ -1228,7 +1228,7 @@
         <x:v>drop:DB1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="AC10" s="8" t="str">
-        <x:v>{"dim":1}</x:v>
+        <x:v>{"backReach":0,"clipRise":0,"dim":1,"note":"CONCEPT: mounted on the 220 mm fixed head band above the door leaves and below the coloured fanlight. E1 remains maintained from DB-1. Product, fixing, visibility and emergency operation require revie"}</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="96" customHeight="1">
@@ -1251,10 +1251,10 @@
         <x:v>34.725</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>4.6</x:v>
+        <x:v>3.061</x:v>
       </x:c>
       <x:c r="H11" s="11" t="n">
-        <x:v>7.245</x:v>
+        <x:v>7.4400000013411045</x:v>
       </x:c>
       <x:c r="I11" s="8" t="str">
         <x:v>wall</x:v>
@@ -1297,7 +1297,7 @@
         <x:v>drop:DB1:E1:light:1:L159</x:v>
       </x:c>
       <x:c r="AC11" s="8" t="str">
-        <x:v>{"dim":1}</x:v>
+        <x:v>{"backReach":0,"clipRise":0,"dim":1,"note":"CONCEPT: mounted on the 220 mm fixed head band above the door leaves and below the coloured fanlight. E1 remains maintained from DB-1. Product, fixing, visibility and emergency operation require revie"}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99f6aec491764623"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0699a86fc43c4523"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1613,8 +1613,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A7,'Route Points'!$F$7:$F$114)</x:f>
-        <x:v>68.67513031117919</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A7,'Route Points'!$F$7:$F$128)</x:f>
+        <x:v>68.64513031028511</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
       <x:c r="K7" s="11" t="str">
@@ -1672,8 +1672,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A8,'Route Points'!$F$7:$F$114)</x:f>
-        <x:v>10.048858786281436</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A8,'Route Points'!$F$7:$F$128)</x:f>
+        <x:v>12.161499905079602</x:v>
       </x:c>
       <x:c r="J8" s="11"/>
       <x:c r="K8" s="11" t="str">
@@ -1690,7 +1690,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P8" s="8" t="str">
-        <x:v>Concealed entrance wall band, solid pier and local termination.</x:v>
+        <x:v>Entrance wall band to solid jamb outside coloured fanlight, fixed transom and local inside-face sign clip. Removable frame cover, fixing and emergency design pending.</x:v>
       </x:c>
       <x:c r="Q8" s="9"/>
       <x:c r="R8" s="9"/>
@@ -1733,8 +1733,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A9,'Route Points'!$F$7:$F$114)</x:f>
-        <x:v>1.503000000000001</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A9,'Route Points'!$F$7:$F$128)</x:f>
+        <x:v>6.9719999986588945</x:v>
       </x:c>
       <x:c r="J9" s="11"/>
       <x:c r="K9" s="11" t="str">
@@ -1751,7 +1751,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P9" s="8" t="str">
-        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+        <x:v>Wall band to solid jamb beside coloured fanlight, fixed 220 mm door-head band and local sign lead. Frame containment, fixing and emergency design pending.</x:v>
       </x:c>
       <x:c r="Q9" s="9"/>
       <x:c r="R9" s="9"/>
@@ -1794,8 +1794,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A10,'Route Points'!$F$7:$F$114)</x:f>
-        <x:v>1.503000000000001</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A10,'Route Points'!$F$7:$F$128)</x:f>
+        <x:v>6.9719999986588945</x:v>
       </x:c>
       <x:c r="J10" s="11"/>
       <x:c r="K10" s="11" t="str">
@@ -1812,7 +1812,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P10" s="8" t="str">
-        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+        <x:v>Wall band to solid jamb beside coloured fanlight, fixed 220 mm door-head band and local sign lead. Frame containment, fixing and emergency design pending.</x:v>
       </x:c>
       <x:c r="Q10" s="9"/>
       <x:c r="R10" s="9"/>
@@ -1856,8 +1856,8 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A11,'Route Points'!$F$7:$F$114)</x:f>
-        <x:v>61.20013031117919</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A11,'Route Points'!$F$7:$F$128)</x:f>
+        <x:v>59.90513031117919</x:v>
       </x:c>
       <x:c r="J11" s="11"/>
       <x:c r="K11" s="11" t="str">
@@ -1915,8 +1915,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A12,'Route Points'!$F$7:$F$114)</x:f>
-        <x:v>1.503000000000001</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A12,'Route Points'!$F$7:$F$128)</x:f>
+        <x:v>6.9719999986588945</x:v>
       </x:c>
       <x:c r="J12" s="11"/>
       <x:c r="K12" s="11" t="str">
@@ -1933,7 +1933,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P12" s="8" t="str">
-        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+        <x:v>Wall band to solid jamb beside coloured fanlight, fixed 220 mm door-head band and local sign lead. Frame containment, fixing and emergency design pending.</x:v>
       </x:c>
       <x:c r="Q12" s="9"/>
       <x:c r="R12" s="9"/>
@@ -1976,8 +1976,8 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A13,'Route Points'!$F$7:$F$114)</x:f>
-        <x:v>1.503000000000001</x:v>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A13,'Route Points'!$F$7:$F$128)</x:f>
+        <x:v>6.9719999986588945</x:v>
       </x:c>
       <x:c r="J13" s="11"/>
       <x:c r="K13" s="11" t="str">
@@ -1994,7 +1994,7 @@
         <x:v>Cable type / conductors / cross-section / conduit: pending electrical design</x:v>
       </x:c>
       <x:c r="P13" s="8" t="str">
-        <x:v>Concealed solid-pier / wall drop and local termination.</x:v>
+        <x:v>Wall band to solid jamb beside coloured fanlight, fixed 220 mm door-head band and local sign lead. Frame containment, fixing and emergency design pending.</x:v>
       </x:c>
       <x:c r="Q13" s="9"/>
       <x:c r="R13" s="9"/>
@@ -2039,7 +2039,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A14,'Route Points'!$F$7:$F$114)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A14,'Route Points'!$F$7:$F$128)</x:f>
         <x:v>69.5751303111792</x:v>
       </x:c>
       <x:c r="J14" s="11"/>
@@ -2098,7 +2098,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A15,'Route Points'!$F$7:$F$114)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A15,'Route Points'!$F$7:$F$128)</x:f>
         <x:v>10.048858786281436</x:v>
       </x:c>
       <x:c r="J15" s="11"/>
@@ -2159,7 +2159,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A16,'Route Points'!$F$7:$F$114)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A16,'Route Points'!$F$7:$F$128)</x:f>
         <x:v>1.503000000000001</x:v>
       </x:c>
       <x:c r="J16" s="11"/>
@@ -2220,7 +2220,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A17,'Route Points'!$F$7:$F$114)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A17,'Route Points'!$F$7:$F$128)</x:f>
         <x:v>1.503000000000001</x:v>
       </x:c>
       <x:c r="J17" s="11"/>
@@ -2282,7 +2282,7 @@
         <x:v>trunk</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A18,'Route Points'!$F$7:$F$114)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A18,'Route Points'!$F$7:$F$128)</x:f>
         <x:v>62.10013031117919</x:v>
       </x:c>
       <x:c r="J18" s="11"/>
@@ -2341,7 +2341,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A19,'Route Points'!$F$7:$F$114)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A19,'Route Points'!$F$7:$F$128)</x:f>
         <x:v>1.503000000000001</x:v>
       </x:c>
       <x:c r="J19" s="11"/>
@@ -2402,7 +2402,7 @@
         <x:v>drop</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:f>SUMIF('Route Points'!$A$7:$A$114,A20,'Route Points'!$F$7:$F$114)</x:f>
+        <x:f>SUMIF('Route Points'!$A$7:$A$128,A20,'Route Points'!$F$7:$F$128)</x:f>
         <x:v>1.503000000000001</x:v>
       </x:c>
       <x:c r="J20" s="11"/>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5faa4abc567940b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a8590e629b64919"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2988,7 +2988,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>2.65</x:v>
+        <x:v>2.6800000008940703</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>5.988</x:v>
@@ -2998,7 +2998,7 @@
       </x:c>
       <x:c r="F25" s="11" t="n">
         <x:f>SQRT((C25-C24)^2+(D25-D24)^2+(E25-E24)^2)</x:f>
-        <x:v>2.8249999999999997</x:v>
+        <x:v>2.7949999991059293</x:v>
       </x:c>
       <x:c r="G25" s="8" t="str">
         <x:v>Current</x:v>
@@ -3012,7 +3012,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
-        <x:v>2.65</x:v>
+        <x:v>2.6800000008940703</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>5.988</x:v>
@@ -3036,17 +3036,17 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>2.5920000008940702</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
         <x:f>SQRT((C27-C26)^2+(D27-D26)^2+(E27-E26)^2)</x:f>
-        <x:v>1.6888587862814344</x:v>
+        <x:v>0.08800000000000008</x:v>
       </x:c>
       <x:c r="G27" s="8" t="str">
         <x:v>Current</x:v>
@@ -3060,17 +3060,17 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>2.5920000008940702</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>7.65</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>1.699999952316284</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
         <x:f>SQRT((C28-C27)^2+(D28-D27)^2+(E28-E27)^2)</x:f>
-        <x:v>7.36</x:v>
+        <x:v>9.059999952316284</x:v>
       </x:c>
       <x:c r="G28" s="8" t="str">
         <x:v>Current</x:v>
@@ -3084,17 +3084,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>2.35</x:v>
+        <x:v>2.5920000008940702</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>6.95</x:v>
+        <x:v>4.9</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>1.699999952316284</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
         <x:f>SQRT((C29-C28)^2+(D29-D28)^2+(E29-E28)^2)</x:f>
-        <x:v>0.7000000000000002</x:v>
+        <x:v>1.088</x:v>
       </x:c>
       <x:c r="G29" s="8" t="str">
         <x:v>Current</x:v>
@@ -3108,17 +3108,17 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>2.65</x:v>
+        <x:v>2.5920000008940702</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>6.95</x:v>
+        <x:v>4.9</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
         <x:f>SQRT((C30-C29)^2+(D30-D29)^2+(E30-E29)^2)</x:f>
-        <x:v>0.2999999999999998</x:v>
+        <x:v>1.699999952316284</x:v>
       </x:c>
       <x:c r="G30" s="8" t="str">
         <x:v>Current</x:v>
@@ -3126,23 +3126,23 @@
     </x:row>
     <x:row r="31" ht="32" customHeight="1">
       <x:c r="A31" s="8" t="str">
-        <x:v>drop:DB1:E1:light:-1:L156</x:v>
+        <x:v>drop:DB1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="B31" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>2.6800000008940703</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>5.988</x:v>
+        <x:v>4.9</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>SQRT((C31-C30)^2+(D31-D30)^2+(E31-E30)^2)</x:f>
+        <x:v>0.08800000000000008</x:v>
       </x:c>
       <x:c r="G31" s="8" t="str">
         <x:v>Current</x:v>
@@ -3150,23 +3150,23 @@
     </x:row>
     <x:row r="32" ht="32" customHeight="1">
       <x:c r="A32" s="8" t="str">
-        <x:v>drop:DB1:E1:light:-1:L156</x:v>
+        <x:v>drop:DB1:E1:light:-1:L155</x:v>
       </x:c>
       <x:c r="B32" s="8" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>2.6800000008940703</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>4.6</x:v>
+        <x:v>4.762499999552966</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
         <x:f>SQRT((C32-C31)^2+(D32-D31)^2+(E32-E31)^2)</x:f>
-        <x:v>1.3880000000000008</x:v>
+        <x:v>0.1375000004470346</x:v>
       </x:c>
       <x:c r="G32" s="8" t="str">
         <x:v>Current</x:v>
@@ -3177,20 +3177,20 @@
         <x:v>drop:DB1:E1:light:-1:L156</x:v>
       </x:c>
       <x:c r="B33" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>18.02</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>4.6</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>-7.245</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
-        <x:f>SQRT((C33-C32)^2+(D33-D32)^2+(E33-E32)^2)</x:f>
-        <x:v>0.11500000000000021</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G33" s="8" t="str">
         <x:v>Current</x:v>
@@ -3198,13 +3198,13 @@
     </x:row>
     <x:row r="34" ht="32" customHeight="1">
       <x:c r="A34" s="8" t="str">
-        <x:v>drop:DB1:E1:light:-1:L158</x:v>
+        <x:v>drop:DB1:E1:light:-1:L156</x:v>
       </x:c>
       <x:c r="B34" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
-        <x:v>34.725</x:v>
+        <x:v>15.450000000000001</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
         <x:v>5.988</x:v>
@@ -3213,152 +3213,152 @@
         <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
+        <x:f>SQRT((C34-C33)^2+(D34-D33)^2+(E34-E33)^2)</x:f>
+        <x:v>2.5699999999999985</x:v>
+      </x:c>
+      <x:c r="G34" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="32" customHeight="1">
+      <x:c r="A35" s="8" t="str">
+        <x:v>drop:DB1:E1:light:-1:L156</x:v>
+      </x:c>
+      <x:c r="B35" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="n">
+        <x:v>15.450000000000001</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="n">
+        <x:v>3.061</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="n">
+        <x:f>SQRT((C35-C34)^2+(D35-D34)^2+(E35-E34)^2)</x:f>
+        <x:v>2.9270000000000005</x:v>
+      </x:c>
+      <x:c r="G35" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="32" customHeight="1">
+      <x:c r="A36" s="8" t="str">
+        <x:v>drop:DB1:E1:light:-1:L156</x:v>
+      </x:c>
+      <x:c r="B36" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="11" t="n">
+        <x:v>15.450000000000001</x:v>
+      </x:c>
+      <x:c r="D36" s="11" t="n">
+        <x:v>3.061</x:v>
+      </x:c>
+      <x:c r="E36" s="11" t="n">
+        <x:v>-7.5</x:v>
+      </x:c>
+      <x:c r="F36" s="11" t="n">
+        <x:f>SQRT((C36-C35)^2+(D36-D35)^2+(E36-E35)^2)</x:f>
+        <x:v>0.13999999999999968</x:v>
+      </x:c>
+      <x:c r="G36" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="32" customHeight="1">
+      <x:c r="A37" s="8" t="str">
+        <x:v>drop:DB1:E1:light:-1:L156</x:v>
+      </x:c>
+      <x:c r="B37" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C37" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D37" s="11" t="n">
+        <x:v>3.061</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="n">
+        <x:v>-7.5</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="n">
+        <x:f>SQRT((C37-C36)^2+(D37-D36)^2+(E37-E36)^2)</x:f>
+        <x:v>1.2750000000000004</x:v>
+      </x:c>
+      <x:c r="G37" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="32" customHeight="1">
+      <x:c r="A38" s="8" t="str">
+        <x:v>drop:DB1:E1:light:-1:L156</x:v>
+      </x:c>
+      <x:c r="B38" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C38" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D38" s="11" t="n">
+        <x:v>3.061</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="n">
+        <x:v>-7.4400000013411045</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="n">
+        <x:f>SQRT((C38-C37)^2+(D38-D37)^2+(E38-E37)^2)</x:f>
+        <x:v>0.05999999865889549</x:v>
+      </x:c>
+      <x:c r="G38" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="32" customHeight="1">
+      <x:c r="A39" s="8" t="str">
+        <x:v>drop:DB1:E1:light:-1:L158</x:v>
+      </x:c>
+      <x:c r="B39" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C39" s="11" t="n">
+        <x:v>36.02</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="32" customHeight="1">
-      <x:c r="A35" s="8" t="str">
-        <x:v>drop:DB1:E1:light:-1:L158</x:v>
-      </x:c>
-      <x:c r="B35" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C35" s="11" t="n">
-        <x:v>34.725</x:v>
-      </x:c>
-      <x:c r="D35" s="11" t="n">
-        <x:v>4.6</x:v>
-      </x:c>
-      <x:c r="E35" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F35" s="11" t="n">
-        <x:f>SQRT((C35-C34)^2+(D35-D34)^2+(E35-E34)^2)</x:f>
-        <x:v>1.3880000000000008</x:v>
-      </x:c>
-      <x:c r="G35" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="32" customHeight="1">
-      <x:c r="A36" s="8" t="str">
-        <x:v>drop:DB1:E1:light:-1:L158</x:v>
-      </x:c>
-      <x:c r="B36" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C36" s="11" t="n">
-        <x:v>34.725</x:v>
-      </x:c>
-      <x:c r="D36" s="11" t="n">
-        <x:v>4.6</x:v>
-      </x:c>
-      <x:c r="E36" s="11" t="n">
-        <x:v>-7.245</x:v>
-      </x:c>
-      <x:c r="F36" s="11" t="n">
-        <x:f>SQRT((C36-C35)^2+(D36-D35)^2+(E36-E35)^2)</x:f>
-        <x:v>0.11500000000000021</x:v>
-      </x:c>
-      <x:c r="G36" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="32" customHeight="1">
-      <x:c r="A37" s="8" t="str">
-        <x:v>trunk:DB1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B37" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C37" s="11" t="n">
-        <x:v>48.895</x:v>
-      </x:c>
-      <x:c r="D37" s="11" t="n">
-        <x:v>1.75</x:v>
-      </x:c>
-      <x:c r="E37" s="11" t="n">
-        <x:v>-1.55</x:v>
-      </x:c>
-      <x:c r="F37" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G37" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="32" customHeight="1">
-      <x:c r="A38" s="8" t="str">
-        <x:v>trunk:DB1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B38" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C38" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D38" s="11" t="n">
-        <x:v>1.75</x:v>
-      </x:c>
-      <x:c r="E38" s="11" t="n">
-        <x:v>-1.55</x:v>
-      </x:c>
-      <x:c r="F38" s="11" t="n">
-        <x:f>SQRT((C38-C37)^2+(D38-D37)^2+(E38-E37)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
-      </x:c>
-      <x:c r="G38" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="32" customHeight="1">
-      <x:c r="A39" s="8" t="str">
-        <x:v>trunk:DB1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B39" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C39" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D39" s="11" t="n">
-        <x:v>1.75</x:v>
-      </x:c>
-      <x:c r="E39" s="11" t="n">
-        <x:v>-2.24</x:v>
-      </x:c>
-      <x:c r="F39" s="11" t="n">
-        <x:f>SQRT((C39-C38)^2+(D39-D38)^2+(E39-E38)^2)</x:f>
-        <x:v>0.6900000000000002</x:v>
-      </x:c>
       <x:c r="G39" s="8" t="str">
         <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="32" customHeight="1">
       <x:c r="A40" s="8" t="str">
-        <x:v>trunk:DB1:E1:light:1</x:v>
+        <x:v>drop:DB1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B40" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>33.45</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>-2.24</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
         <x:f>SQRT((C40-C39)^2+(D40-D39)^2+(E40-E39)^2)</x:f>
-        <x:v>2.58</x:v>
+        <x:v>2.5700000000000003</x:v>
       </x:c>
       <x:c r="G40" s="8" t="str">
         <x:v>Current</x:v>
@@ -3366,23 +3366,23 @@
     </x:row>
     <x:row r="41" ht="32" customHeight="1">
       <x:c r="A41" s="8" t="str">
-        <x:v>trunk:DB1:E1:light:1</x:v>
+        <x:v>drop:DB1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B41" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
-        <x:v>48.735</x:v>
+        <x:v>33.45</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>3.061</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
         <x:f>SQRT((C41-C40)^2+(D41-D40)^2+(E41-E40)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
+        <x:v>2.9270000000000005</x:v>
       </x:c>
       <x:c r="G41" s="8" t="str">
         <x:v>Current</x:v>
@@ -3390,23 +3390,23 @@
     </x:row>
     <x:row r="42" ht="32" customHeight="1">
       <x:c r="A42" s="8" t="str">
-        <x:v>trunk:DB1:E1:light:1</x:v>
+        <x:v>drop:DB1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B42" s="8" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>33.45</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>4.33</x:v>
+        <x:v>3.061</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.5</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
         <x:f>SQRT((C42-C41)^2+(D42-D41)^2+(E42-E41)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
+        <x:v>0.13999999999999968</x:v>
       </x:c>
       <x:c r="G42" s="8" t="str">
         <x:v>Current</x:v>
@@ -3414,23 +3414,23 @@
     </x:row>
     <x:row r="43" ht="32" customHeight="1">
       <x:c r="A43" s="8" t="str">
-        <x:v>trunk:DB1:E1:light:1</x:v>
+        <x:v>drop:DB1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B43" s="8" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>5.988</x:v>
+        <x:v>3.061</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:v>-3.3</x:v>
+        <x:v>-7.5</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
         <x:f>SQRT((C43-C42)^2+(D43-D42)^2+(E43-E42)^2)</x:f>
-        <x:v>1.6580000000000004</x:v>
+        <x:v>1.2749999999999986</x:v>
       </x:c>
       <x:c r="G43" s="8" t="str">
         <x:v>Current</x:v>
@@ -3438,23 +3438,23 @@
     </x:row>
     <x:row r="44" ht="32" customHeight="1">
       <x:c r="A44" s="8" t="str">
-        <x:v>trunk:DB1:E1:light:1</x:v>
+        <x:v>drop:DB1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B44" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
-        <x:v>53.016</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>5.988</x:v>
+        <x:v>3.061</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.4400000013411045</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
         <x:f>SQRT((C44-C43)^2+(D44-D43)^2+(E44-E43)^2)</x:f>
-        <x:v>10.66</x:v>
+        <x:v>0.05999999865889549</x:v>
       </x:c>
       <x:c r="G44" s="8" t="str">
         <x:v>Current</x:v>
@@ -3465,20 +3465,20 @@
         <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B45" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>5.988</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:f>SQRT((C45-C44)^2+(D45-D44)^2+(E45-E44)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G45" s="8" t="str">
         <x:v>Current</x:v>
@@ -3489,20 +3489,20 @@
         <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B46" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
         <x:f>SQRT((C46-C45)^2+(D46-D45)^2+(E46-E45)^2)</x:f>
-        <x:v>1.0519999999999996</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G46" s="8" t="str">
         <x:v>Current</x:v>
@@ -3513,20 +3513,20 @@
         <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B47" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C47" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D47" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F47" s="11" t="n">
         <x:f>SQRT((C47-C46)^2+(D47-D46)^2+(E47-E46)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.6900000000000002</x:v>
       </x:c>
       <x:c r="G47" s="8" t="str">
         <x:v>Current</x:v>
@@ -3537,20 +3537,20 @@
         <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B48" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D48" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
         <x:f>SQRT((C48-C47)^2+(D48-D47)^2+(E48-E47)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>2.58</x:v>
       </x:c>
       <x:c r="G48" s="8" t="str">
         <x:v>Current</x:v>
@@ -3561,20 +3561,20 @@
         <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B49" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C49" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D49" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
         <x:f>SQRT((C49-C48)^2+(D49-D48)^2+(E49-E48)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G49" s="8" t="str">
         <x:v>Current</x:v>
@@ -3585,20 +3585,20 @@
         <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B50" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C50" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D50" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E50" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F50" s="11" t="n">
         <x:f>SQRT((C50-C49)^2+(D50-D49)^2+(E50-E49)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>4.280999999999999</x:v>
       </x:c>
       <x:c r="G50" s="8" t="str">
         <x:v>Current</x:v>
@@ -3609,20 +3609,20 @@
         <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B51" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C51" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D51" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E51" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F51" s="11" t="n">
         <x:f>SQRT((C51-C50)^2+(D51-D50)^2+(E51-E50)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:v>1.6580000000000004</x:v>
       </x:c>
       <x:c r="G51" s="8" t="str">
         <x:v>Current</x:v>
@@ -3633,20 +3633,20 @@
         <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B52" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C52" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>53.016</x:v>
       </x:c>
       <x:c r="D52" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E52" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F52" s="11" t="n">
         <x:f>SQRT((C52-C51)^2+(D52-D51)^2+(E52-E51)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>10.66</x:v>
       </x:c>
       <x:c r="G52" s="8" t="str">
         <x:v>Current</x:v>
@@ -3657,10 +3657,10 @@
         <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B53" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C53" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D53" s="11" t="n">
         <x:v>5.988</x:v>
@@ -3670,7 +3670,7 @@
       </x:c>
       <x:c r="F53" s="11" t="n">
         <x:f>SQRT((C53-C52)^2+(D53-D52)^2+(E53-E52)^2)</x:f>
-        <x:v>1.0519999999999996</x:v>
+        <x:v>8.841000000000001</x:v>
       </x:c>
       <x:c r="G53" s="8" t="str">
         <x:v>Current</x:v>
@@ -3681,20 +3681,20 @@
         <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B54" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C54" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>44.175</x:v>
       </x:c>
       <x:c r="D54" s="11" t="n">
-        <x:v>5.988</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E54" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F54" s="11" t="n">
         <x:f>SQRT((C54-C53)^2+(D54-D53)^2+(E54-E53)^2)</x:f>
-        <x:v>20.25</x:v>
+        <x:v>1.0519999999999996</x:v>
       </x:c>
       <x:c r="G54" s="8" t="str">
         <x:v>Current</x:v>
@@ -3702,482 +3702,482 @@
     </x:row>
     <x:row r="55" ht="32" customHeight="1">
       <x:c r="A55" s="8" t="str">
-        <x:v>drop:DB1:E1:light:1:L157</x:v>
+        <x:v>trunk:DB1:E1:light:1</x:v>
       </x:c>
       <x:c r="B55" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C55" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>43.535</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
-        <x:v>5.988</x:v>
+        <x:v>7.04</x:v>
       </x:c>
       <x:c r="E55" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
       <x:c r="F55" s="11" t="n">
+        <x:f>SQRT((C55-C54)^2+(D55-D54)^2+(E55-E54)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G55" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="32" customHeight="1">
+      <x:c r="A56" s="8" t="str">
+        <x:v>trunk:DB1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B56" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C56" s="11" t="n">
+        <x:v>43.455</x:v>
+      </x:c>
+      <x:c r="D56" s="11" t="n">
+        <x:v>6.950412371134024</x:v>
+      </x:c>
+      <x:c r="E56" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F56" s="11" t="n">
+        <x:f>SQRT((C56-C55)^2+(D56-D55)^2+(E56-E55)^2)</x:f>
+        <x:v>0.12010804821421249</x:v>
+      </x:c>
+      <x:c r="G56" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="32" customHeight="1">
+      <x:c r="A57" s="8" t="str">
+        <x:v>trunk:DB1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B57" s="8" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C57" s="11" t="n">
+        <x:v>40.574999999999996</x:v>
+      </x:c>
+      <x:c r="D57" s="11" t="n">
+        <x:v>9.269999999999994</x:v>
+      </x:c>
+      <x:c r="E57" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F57" s="11" t="n">
+        <x:f>SQRT((C57-C56)^2+(D57-D56)^2+(E57-E56)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
+      </x:c>
+      <x:c r="G57" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="32" customHeight="1">
+      <x:c r="A58" s="8" t="str">
+        <x:v>trunk:DB1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B58" s="8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C58" s="11" t="n">
+        <x:v>37.695</x:v>
+      </x:c>
+      <x:c r="D58" s="11" t="n">
+        <x:v>6.950412371134018</x:v>
+      </x:c>
+      <x:c r="E58" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F58" s="11" t="n">
+        <x:f>SQRT((C58-C57)^2+(D58-D57)^2+(E58-E57)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
+      </x:c>
+      <x:c r="G58" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="32" customHeight="1">
+      <x:c r="A59" s="8" t="str">
+        <x:v>trunk:DB1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B59" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C59" s="11" t="n">
+        <x:v>37.615</x:v>
+      </x:c>
+      <x:c r="D59" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E59" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F59" s="11" t="n">
+        <x:f>SQRT((C59-C58)^2+(D59-D58)^2+(E59-E58)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
+      </x:c>
+      <x:c r="G59" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="32" customHeight="1">
+      <x:c r="A60" s="8" t="str">
+        <x:v>trunk:DB1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B60" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C60" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D60" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E60" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F60" s="11" t="n">
+        <x:f>SQRT((C60-C59)^2+(D60-D59)^2+(E60-E59)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G60" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="32" customHeight="1">
+      <x:c r="A61" s="8" t="str">
+        <x:v>trunk:DB1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B61" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C61" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D61" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E61" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F61" s="11" t="n">
+        <x:f>SQRT((C61-C60)^2+(D61-D60)^2+(E61-E60)^2)</x:f>
+        <x:v>1.0519999999999996</x:v>
+      </x:c>
+      <x:c r="G61" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="32" customHeight="1">
+      <x:c r="A62" s="8" t="str">
+        <x:v>trunk:DB1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B62" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C62" s="11" t="n">
+        <x:v>18.02</x:v>
+      </x:c>
+      <x:c r="D62" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E62" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F62" s="11" t="n">
+        <x:f>SQRT((C62-C61)^2+(D62-D61)^2+(E62-E61)^2)</x:f>
+        <x:v>18.955000000000002</x:v>
+      </x:c>
+      <x:c r="G62" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="32" customHeight="1">
+      <x:c r="A63" s="8" t="str">
+        <x:v>drop:DB1:E1:light:1:L157</x:v>
+      </x:c>
+      <x:c r="B63" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C63" s="11" t="n">
+        <x:v>18.02</x:v>
+      </x:c>
+      <x:c r="D63" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E63" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F63" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G55" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" ht="32" customHeight="1">
-      <x:c r="A56" s="8" t="str">
+      <x:c r="G63" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="32" customHeight="1">
+      <x:c r="A64" s="8" t="str">
         <x:v>drop:DB1:E1:light:1:L157</x:v>
       </x:c>
-      <x:c r="B56" s="8" t="n">
+      <x:c r="B64" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C56" s="11" t="n">
+      <x:c r="C64" s="11" t="n">
+        <x:v>15.450000000000001</x:v>
+      </x:c>
+      <x:c r="D64" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E64" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F64" s="11" t="n">
+        <x:f>SQRT((C64-C63)^2+(D64-D63)^2+(E64-E63)^2)</x:f>
+        <x:v>2.5699999999999985</x:v>
+      </x:c>
+      <x:c r="G64" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="32" customHeight="1">
+      <x:c r="A65" s="8" t="str">
+        <x:v>drop:DB1:E1:light:1:L157</x:v>
+      </x:c>
+      <x:c r="B65" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C65" s="11" t="n">
+        <x:v>15.450000000000001</x:v>
+      </x:c>
+      <x:c r="D65" s="11" t="n">
+        <x:v>3.061</x:v>
+      </x:c>
+      <x:c r="E65" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F65" s="11" t="n">
+        <x:f>SQRT((C65-C64)^2+(D65-D64)^2+(E65-E64)^2)</x:f>
+        <x:v>2.9270000000000005</x:v>
+      </x:c>
+      <x:c r="G65" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="32" customHeight="1">
+      <x:c r="A66" s="8" t="str">
+        <x:v>drop:DB1:E1:light:1:L157</x:v>
+      </x:c>
+      <x:c r="B66" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C66" s="11" t="n">
+        <x:v>15.450000000000001</x:v>
+      </x:c>
+      <x:c r="D66" s="11" t="n">
+        <x:v>3.061</x:v>
+      </x:c>
+      <x:c r="E66" s="11" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="F66" s="11" t="n">
+        <x:f>SQRT((C66-C65)^2+(D66-D65)^2+(E66-E65)^2)</x:f>
+        <x:v>0.13999999999999968</x:v>
+      </x:c>
+      <x:c r="G66" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="32" customHeight="1">
+      <x:c r="A67" s="8" t="str">
+        <x:v>drop:DB1:E1:light:1:L157</x:v>
+      </x:c>
+      <x:c r="B67" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C67" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
-      <x:c r="D56" s="11" t="n">
-        <x:v>4.6</x:v>
-      </x:c>
-      <x:c r="E56" s="11" t="n">
+      <x:c r="D67" s="11" t="n">
+        <x:v>3.061</x:v>
+      </x:c>
+      <x:c r="E67" s="11" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="F67" s="11" t="n">
+        <x:f>SQRT((C67-C66)^2+(D67-D66)^2+(E67-E66)^2)</x:f>
+        <x:v>1.2750000000000004</x:v>
+      </x:c>
+      <x:c r="G67" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="32" customHeight="1">
+      <x:c r="A68" s="8" t="str">
+        <x:v>drop:DB1:E1:light:1:L157</x:v>
+      </x:c>
+      <x:c r="B68" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C68" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D68" s="11" t="n">
+        <x:v>3.061</x:v>
+      </x:c>
+      <x:c r="E68" s="11" t="n">
+        <x:v>7.4400000013411045</x:v>
+      </x:c>
+      <x:c r="F68" s="11" t="n">
+        <x:f>SQRT((C68-C67)^2+(D68-D67)^2+(E68-E67)^2)</x:f>
+        <x:v>0.05999999865889549</x:v>
+      </x:c>
+      <x:c r="G68" s="8" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="32" customHeight="1">
+      <x:c r="A69" s="8" t="str">
+        <x:v>drop:DB1:E1:light:1:L159</x:v>
+      </x:c>
+      <x:c r="B69" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C69" s="11" t="n">
+        <x:v>36.02</x:v>
+      </x:c>
+      <x:c r="D69" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E69" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F56" s="11" t="n">
-        <x:f>SQRT((C56-C55)^2+(D56-D55)^2+(E56-E55)^2)</x:f>
-        <x:v>1.3880000000000008</x:v>
-      </x:c>
-      <x:c r="G56" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="32" customHeight="1">
-      <x:c r="A57" s="8" t="str">
-        <x:v>drop:DB1:E1:light:1:L157</x:v>
-      </x:c>
-      <x:c r="B57" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C57" s="11" t="n">
-        <x:v>16.725</x:v>
-      </x:c>
-      <x:c r="D57" s="11" t="n">
-        <x:v>4.6</x:v>
-      </x:c>
-      <x:c r="E57" s="11" t="n">
-        <x:v>7.245</x:v>
-      </x:c>
-      <x:c r="F57" s="11" t="n">
-        <x:f>SQRT((C57-C56)^2+(D57-D56)^2+(E57-E56)^2)</x:f>
-        <x:v>0.11500000000000021</x:v>
-      </x:c>
-      <x:c r="G57" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" ht="32" customHeight="1">
-      <x:c r="A58" s="8" t="str">
-        <x:v>drop:DB1:E1:light:1:L159</x:v>
-      </x:c>
-      <x:c r="B58" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C58" s="11" t="n">
-        <x:v>34.725</x:v>
-      </x:c>
-      <x:c r="D58" s="11" t="n">
-        <x:v>5.988</x:v>
-      </x:c>
-      <x:c r="E58" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F58" s="11" t="n">
+      <x:c r="F69" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G58" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="32" customHeight="1">
-      <x:c r="A59" s="8" t="str">
-        <x:v>drop:DB1:E1:light:1:L159</x:v>
-      </x:c>
-      <x:c r="B59" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C59" s="11" t="n">
-        <x:v>34.725</x:v>
-      </x:c>
-      <x:c r="D59" s="11" t="n">
-        <x:v>4.6</x:v>
-      </x:c>
-      <x:c r="E59" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F59" s="11" t="n">
-        <x:f>SQRT((C59-C58)^2+(D59-D58)^2+(E59-E58)^2)</x:f>
-        <x:v>1.3880000000000008</x:v>
-      </x:c>
-      <x:c r="G59" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" ht="32" customHeight="1">
-      <x:c r="A60" s="8" t="str">
-        <x:v>drop:DB1:E1:light:1:L159</x:v>
-      </x:c>
-      <x:c r="B60" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C60" s="11" t="n">
-        <x:v>34.725</x:v>
-      </x:c>
-      <x:c r="D60" s="11" t="n">
-        <x:v>4.6</x:v>
-      </x:c>
-      <x:c r="E60" s="11" t="n">
-        <x:v>7.245</x:v>
-      </x:c>
-      <x:c r="F60" s="11" t="n">
-        <x:f>SQRT((C60-C59)^2+(D60-D59)^2+(E60-E59)^2)</x:f>
-        <x:v>0.11500000000000021</x:v>
-      </x:c>
-      <x:c r="G60" s="8" t="str">
-        <x:v>Current</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" ht="32" customHeight="1">
-      <x:c r="A61" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
-      </x:c>
-      <x:c r="B61" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C61" s="11" t="n">
-        <x:v>48.895</x:v>
-      </x:c>
-      <x:c r="D61" s="11" t="n">
-        <x:v>1.85</x:v>
-      </x:c>
-      <x:c r="E61" s="11" t="n">
-        <x:v>-0.55</x:v>
-      </x:c>
-      <x:c r="F61" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G61" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="32" customHeight="1">
-      <x:c r="A62" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
-      </x:c>
-      <x:c r="B62" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C62" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D62" s="11" t="n">
-        <x:v>1.85</x:v>
-      </x:c>
-      <x:c r="E62" s="11" t="n">
-        <x:v>-0.55</x:v>
-      </x:c>
-      <x:c r="F62" s="11" t="n">
-        <x:f>SQRT((C62-C61)^2+(D62-D61)^2+(E62-E61)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
-      </x:c>
-      <x:c r="G62" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" ht="32" customHeight="1">
-      <x:c r="A63" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
-      </x:c>
-      <x:c r="B63" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C63" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D63" s="11" t="n">
-        <x:v>1.85</x:v>
-      </x:c>
-      <x:c r="E63" s="11" t="n">
-        <x:v>-2.24</x:v>
-      </x:c>
-      <x:c r="F63" s="11" t="n">
-        <x:f>SQRT((C63-C62)^2+(D63-D62)^2+(E63-E62)^2)</x:f>
-        <x:v>1.6900000000000002</x:v>
-      </x:c>
-      <x:c r="G63" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="32" customHeight="1">
-      <x:c r="A64" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
-      </x:c>
-      <x:c r="B64" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C64" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D64" s="11" t="n">
-        <x:v>4.33</x:v>
-      </x:c>
-      <x:c r="E64" s="11" t="n">
-        <x:v>-2.24</x:v>
-      </x:c>
-      <x:c r="F64" s="11" t="n">
-        <x:f>SQRT((C64-C63)^2+(D64-D63)^2+(E64-E63)^2)</x:f>
-        <x:v>2.48</x:v>
-      </x:c>
-      <x:c r="G64" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="32" customHeight="1">
-      <x:c r="A65" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
-      </x:c>
-      <x:c r="B65" s="8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C65" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D65" s="11" t="n">
-        <x:v>4.33</x:v>
-      </x:c>
-      <x:c r="E65" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F65" s="11" t="n">
-        <x:f>SQRT((C65-C64)^2+(D65-D64)^2+(E65-E64)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
-      </x:c>
-      <x:c r="G65" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" ht="32" customHeight="1">
-      <x:c r="A66" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
-      </x:c>
-      <x:c r="B66" s="8" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C66" s="11" t="n">
-        <x:v>53.016</x:v>
-      </x:c>
-      <x:c r="D66" s="11" t="n">
-        <x:v>4.33</x:v>
-      </x:c>
-      <x:c r="E66" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F66" s="11" t="n">
-        <x:f>SQRT((C66-C65)^2+(D66-D65)^2+(E66-E65)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
-      </x:c>
-      <x:c r="G66" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" ht="32" customHeight="1">
-      <x:c r="A67" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
-      </x:c>
-      <x:c r="B67" s="8" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C67" s="11" t="n">
-        <x:v>53.016</x:v>
-      </x:c>
-      <x:c r="D67" s="11" t="n">
-        <x:v>5.988</x:v>
-      </x:c>
-      <x:c r="E67" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F67" s="11" t="n">
-        <x:f>SQRT((C67-C66)^2+(D67-D66)^2+(E67-E66)^2)</x:f>
-        <x:v>1.6580000000000004</x:v>
-      </x:c>
-      <x:c r="G67" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" ht="32" customHeight="1">
-      <x:c r="A68" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
-      </x:c>
-      <x:c r="B68" s="8" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C68" s="11" t="n">
-        <x:v>53.016</x:v>
-      </x:c>
-      <x:c r="D68" s="11" t="n">
-        <x:v>5.988</x:v>
-      </x:c>
-      <x:c r="E68" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F68" s="11" t="n">
-        <x:f>SQRT((C68-C67)^2+(D68-D67)^2+(E68-E67)^2)</x:f>
-        <x:v>4.0600000000000005</x:v>
-      </x:c>
-      <x:c r="G68" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" ht="32" customHeight="1">
-      <x:c r="A69" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
-      </x:c>
-      <x:c r="B69" s="8" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C69" s="11" t="n">
-        <x:v>44.175</x:v>
-      </x:c>
-      <x:c r="D69" s="11" t="n">
-        <x:v>5.988</x:v>
-      </x:c>
-      <x:c r="E69" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F69" s="11" t="n">
-        <x:f>SQRT((C69-C68)^2+(D69-D68)^2+(E69-E68)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
-      </x:c>
       <x:c r="G69" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="32" customHeight="1">
       <x:c r="A70" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>drop:DB1:E1:light:1:L159</x:v>
       </x:c>
       <x:c r="B70" s="8" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C70" s="11" t="n">
-        <x:v>44.175</x:v>
+        <x:v>33.45</x:v>
       </x:c>
       <x:c r="D70" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>5.988</x:v>
       </x:c>
       <x:c r="E70" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F70" s="11" t="n">
         <x:f>SQRT((C70-C69)^2+(D70-D69)^2+(E70-E69)^2)</x:f>
-        <x:v>1.0519999999999996</x:v>
+        <x:v>2.5700000000000003</x:v>
       </x:c>
       <x:c r="G70" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="32" customHeight="1">
       <x:c r="A71" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>drop:DB1:E1:light:1:L159</x:v>
       </x:c>
       <x:c r="B71" s="8" t="n">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C71" s="11" t="n">
-        <x:v>43.535</x:v>
+        <x:v>33.45</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>3.061</x:v>
       </x:c>
       <x:c r="E71" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.36</x:v>
       </x:c>
       <x:c r="F71" s="11" t="n">
         <x:f>SQRT((C71-C70)^2+(D71-D70)^2+(E71-E70)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>2.9270000000000005</x:v>
       </x:c>
       <x:c r="G71" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="32" customHeight="1">
       <x:c r="A72" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>drop:DB1:E1:light:1:L159</x:v>
       </x:c>
       <x:c r="B72" s="8" t="n">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C72" s="11" t="n">
-        <x:v>43.455</x:v>
+        <x:v>33.45</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
+        <x:v>3.061</x:v>
       </x:c>
       <x:c r="E72" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="F72" s="11" t="n">
         <x:f>SQRT((C72-C71)^2+(D72-D71)^2+(E72-E71)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
+        <x:v>0.13999999999999968</x:v>
       </x:c>
       <x:c r="G72" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="32" customHeight="1">
       <x:c r="A73" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>drop:DB1:E1:light:1:L159</x:v>
       </x:c>
       <x:c r="B73" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C73" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D73" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>3.061</x:v>
       </x:c>
       <x:c r="E73" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.5</x:v>
       </x:c>
       <x:c r="F73" s="11" t="n">
         <x:f>SQRT((C73-C72)^2+(D73-D72)^2+(E73-E72)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>1.2749999999999986</x:v>
       </x:c>
       <x:c r="G73" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="32" customHeight="1">
       <x:c r="A74" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:-1</x:v>
+        <x:v>drop:DB1:E1:light:1:L159</x:v>
       </x:c>
       <x:c r="B74" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C74" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D74" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>3.061</x:v>
       </x:c>
       <x:c r="E74" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>7.4400000013411045</x:v>
       </x:c>
       <x:c r="F74" s="11" t="n">
         <x:f>SQRT((C74-C73)^2+(D74-D73)^2+(E74-E73)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>0.05999999865889549</x:v>
       </x:c>
       <x:c r="G74" s="8" t="str">
-        <x:v>Retired</x:v>
+        <x:v>Current</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="32" customHeight="1">
@@ -4185,20 +4185,20 @@
         <x:v>trunk:LC1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B75" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C75" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D75" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E75" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="F75" s="11" t="n">
-        <x:f>SQRT((C75-C74)^2+(D75-D74)^2+(E75-E74)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G75" s="8" t="str">
         <x:v>Retired</x:v>
@@ -4209,20 +4209,20 @@
         <x:v>trunk:LC1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B76" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C76" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D76" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E76" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="F76" s="11" t="n">
         <x:f>SQRT((C76-C75)^2+(D76-D75)^2+(E76-E75)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G76" s="8" t="str">
         <x:v>Retired</x:v>
@@ -4233,20 +4233,20 @@
         <x:v>trunk:LC1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B77" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C77" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D77" s="11" t="n">
-        <x:v>5.988</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E77" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F77" s="11" t="n">
         <x:f>SQRT((C77-C76)^2+(D77-D76)^2+(E77-E76)^2)</x:f>
-        <x:v>1.0519999999999996</x:v>
+        <x:v>1.6900000000000002</x:v>
       </x:c>
       <x:c r="G77" s="8" t="str">
         <x:v>Retired</x:v>
@@ -4257,20 +4257,20 @@
         <x:v>trunk:LC1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B78" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C78" s="11" t="n">
-        <x:v>5.475</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
-        <x:v>5.988</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E78" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F78" s="11" t="n">
         <x:f>SQRT((C78-C77)^2+(D78-D77)^2+(E78-E77)^2)</x:f>
-        <x:v>31.5</x:v>
+        <x:v>2.48</x:v>
       </x:c>
       <x:c r="G78" s="8" t="str">
         <x:v>Retired</x:v>
@@ -4281,20 +4281,20 @@
         <x:v>trunk:LC1:E1:light:-1</x:v>
       </x:c>
       <x:c r="B79" s="8" t="n">
-        <x:v>19</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C79" s="11" t="n">
-        <x:v>2.65</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
-        <x:v>5.988</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E79" s="11" t="n">
-        <x:v>-7.36</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="F79" s="11" t="n">
         <x:f>SQRT((C79-C78)^2+(D79-D78)^2+(E79-E78)^2)</x:f>
-        <x:v>2.8249999999999997</x:v>
+        <x:v>1.0599999999999996</x:v>
       </x:c>
       <x:c r="G79" s="8" t="str">
         <x:v>Retired</x:v>
@@ -4302,575 +4302,575 @@
     </x:row>
     <x:row r="80" ht="32" customHeight="1">
       <x:c r="A80" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B80" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C80" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D80" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E80" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F80" s="11" t="n">
+        <x:f>SQRT((C80-C79)^2+(D80-D79)^2+(E80-E79)^2)</x:f>
+        <x:v>4.280999999999999</x:v>
+      </x:c>
+      <x:c r="G80" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="32" customHeight="1">
+      <x:c r="A81" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B81" s="8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C81" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D81" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E81" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F81" s="11" t="n">
+        <x:f>SQRT((C81-C80)^2+(D81-D80)^2+(E81-E80)^2)</x:f>
+        <x:v>1.6580000000000004</x:v>
+      </x:c>
+      <x:c r="G81" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="32" customHeight="1">
+      <x:c r="A82" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B82" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C82" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D82" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E82" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F82" s="11" t="n">
+        <x:f>SQRT((C82-C81)^2+(D82-D81)^2+(E82-E81)^2)</x:f>
+        <x:v>4.0600000000000005</x:v>
+      </x:c>
+      <x:c r="G82" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="32" customHeight="1">
+      <x:c r="A83" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B83" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C83" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D83" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E83" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F83" s="11" t="n">
+        <x:f>SQRT((C83-C82)^2+(D83-D82)^2+(E83-E82)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
+      </x:c>
+      <x:c r="G83" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="32" customHeight="1">
+      <x:c r="A84" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B84" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C84" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D84" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E84" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F84" s="11" t="n">
+        <x:f>SQRT((C84-C83)^2+(D84-D83)^2+(E84-E83)^2)</x:f>
+        <x:v>1.0519999999999996</x:v>
+      </x:c>
+      <x:c r="G84" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="32" customHeight="1">
+      <x:c r="A85" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B85" s="8" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C85" s="11" t="n">
+        <x:v>43.535</x:v>
+      </x:c>
+      <x:c r="D85" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E85" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F85" s="11" t="n">
+        <x:f>SQRT((C85-C84)^2+(D85-D84)^2+(E85-E84)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G85" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="32" customHeight="1">
+      <x:c r="A86" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B86" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C86" s="11" t="n">
+        <x:v>43.455</x:v>
+      </x:c>
+      <x:c r="D86" s="11" t="n">
+        <x:v>6.950412371134024</x:v>
+      </x:c>
+      <x:c r="E86" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F86" s="11" t="n">
+        <x:f>SQRT((C86-C85)^2+(D86-D85)^2+(E86-E85)^2)</x:f>
+        <x:v>0.12010804821421249</x:v>
+      </x:c>
+      <x:c r="G86" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="32" customHeight="1">
+      <x:c r="A87" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B87" s="8" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C87" s="11" t="n">
+        <x:v>40.574999999999996</x:v>
+      </x:c>
+      <x:c r="D87" s="11" t="n">
+        <x:v>9.269999999999994</x:v>
+      </x:c>
+      <x:c r="E87" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F87" s="11" t="n">
+        <x:f>SQRT((C87-C86)^2+(D87-D86)^2+(E87-E86)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
+      </x:c>
+      <x:c r="G87" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="32" customHeight="1">
+      <x:c r="A88" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B88" s="8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C88" s="11" t="n">
+        <x:v>37.695</x:v>
+      </x:c>
+      <x:c r="D88" s="11" t="n">
+        <x:v>6.950412371134018</x:v>
+      </x:c>
+      <x:c r="E88" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F88" s="11" t="n">
+        <x:f>SQRT((C88-C87)^2+(D88-D87)^2+(E88-E87)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
+      </x:c>
+      <x:c r="G88" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="32" customHeight="1">
+      <x:c r="A89" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B89" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C89" s="11" t="n">
+        <x:v>37.615</x:v>
+      </x:c>
+      <x:c r="D89" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E89" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F89" s="11" t="n">
+        <x:f>SQRT((C89-C88)^2+(D89-D88)^2+(E89-E88)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
+      </x:c>
+      <x:c r="G89" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="32" customHeight="1">
+      <x:c r="A90" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B90" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C90" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D90" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E90" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F90" s="11" t="n">
+        <x:f>SQRT((C90-C89)^2+(D90-D89)^2+(E90-E89)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G90" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="32" customHeight="1">
+      <x:c r="A91" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B91" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C91" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D91" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E91" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F91" s="11" t="n">
+        <x:f>SQRT((C91-C90)^2+(D91-D90)^2+(E91-E90)^2)</x:f>
+        <x:v>1.0519999999999996</x:v>
+      </x:c>
+      <x:c r="G91" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="32" customHeight="1">
+      <x:c r="A92" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B92" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C92" s="11" t="n">
+        <x:v>5.475</x:v>
+      </x:c>
+      <x:c r="D92" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E92" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F92" s="11" t="n">
+        <x:f>SQRT((C92-C91)^2+(D92-D91)^2+(E92-E91)^2)</x:f>
+        <x:v>31.5</x:v>
+      </x:c>
+      <x:c r="G92" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="32" customHeight="1">
+      <x:c r="A93" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:-1</x:v>
+      </x:c>
+      <x:c r="B93" s="8" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C93" s="11" t="n">
+        <x:v>2.65</x:v>
+      </x:c>
+      <x:c r="D93" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E93" s="11" t="n">
+        <x:v>-7.36</x:v>
+      </x:c>
+      <x:c r="F93" s="11" t="n">
+        <x:f>SQRT((C93-C92)^2+(D93-D92)^2+(E93-E92)^2)</x:f>
+        <x:v>2.8249999999999997</x:v>
+      </x:c>
+      <x:c r="G93" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="32" customHeight="1">
+      <x:c r="A94" s="8" t="str">
         <x:v>drop:LC1:E1:light:-1:L155</x:v>
       </x:c>
-      <x:c r="B80" s="8" t="n">
+      <x:c r="B94" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C80" s="11" t="n">
+      <x:c r="C94" s="11" t="n">
         <x:v>2.65</x:v>
       </x:c>
-      <x:c r="D80" s="11" t="n">
+      <x:c r="D94" s="11" t="n">
         <x:v>5.988</x:v>
       </x:c>
-      <x:c r="E80" s="11" t="n">
+      <x:c r="E94" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
-      <x:c r="F80" s="11" t="n">
+      <x:c r="F94" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G80" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="32" customHeight="1">
-      <x:c r="A81" s="8" t="str">
+      <x:c r="G94" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="32" customHeight="1">
+      <x:c r="A95" s="8" t="str">
         <x:v>drop:LC1:E1:light:-1:L155</x:v>
       </x:c>
-      <x:c r="B81" s="8" t="n">
+      <x:c r="B95" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C81" s="11" t="n">
+      <x:c r="C95" s="11" t="n">
         <x:v>2.35</x:v>
       </x:c>
-      <x:c r="D81" s="11" t="n">
+      <x:c r="D95" s="11" t="n">
         <x:v>7.65</x:v>
       </x:c>
-      <x:c r="E81" s="11" t="n">
+      <x:c r="E95" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
-      <x:c r="F81" s="11" t="n">
-        <x:f>SQRT((C81-C80)^2+(D81-D80)^2+(E81-E80)^2)</x:f>
+      <x:c r="F95" s="11" t="n">
+        <x:f>SQRT((C95-C94)^2+(D95-D94)^2+(E95-E94)^2)</x:f>
         <x:v>1.6888587862814344</x:v>
       </x:c>
-      <x:c r="G81" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" ht="32" customHeight="1">
-      <x:c r="A82" s="8" t="str">
+      <x:c r="G95" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="32" customHeight="1">
+      <x:c r="A96" s="8" t="str">
         <x:v>drop:LC1:E1:light:-1:L155</x:v>
       </x:c>
-      <x:c r="B82" s="8" t="n">
+      <x:c r="B96" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C82" s="11" t="n">
+      <x:c r="C96" s="11" t="n">
         <x:v>2.35</x:v>
       </x:c>
-      <x:c r="D82" s="11" t="n">
+      <x:c r="D96" s="11" t="n">
         <x:v>7.65</x:v>
       </x:c>
-      <x:c r="E82" s="11" t="n">
+      <x:c r="E96" s="11" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F82" s="11" t="n">
-        <x:f>SQRT((C82-C81)^2+(D82-D81)^2+(E82-E81)^2)</x:f>
+      <x:c r="F96" s="11" t="n">
+        <x:f>SQRT((C96-C95)^2+(D96-D95)^2+(E96-E95)^2)</x:f>
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="G82" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" ht="32" customHeight="1">
-      <x:c r="A83" s="8" t="str">
+      <x:c r="G96" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="32" customHeight="1">
+      <x:c r="A97" s="8" t="str">
         <x:v>drop:LC1:E1:light:-1:L155</x:v>
       </x:c>
-      <x:c r="B83" s="8" t="n">
+      <x:c r="B97" s="8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C83" s="11" t="n">
+      <x:c r="C97" s="11" t="n">
         <x:v>2.35</x:v>
       </x:c>
-      <x:c r="D83" s="11" t="n">
+      <x:c r="D97" s="11" t="n">
         <x:v>6.95</x:v>
       </x:c>
-      <x:c r="E83" s="11" t="n">
+      <x:c r="E97" s="11" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F83" s="11" t="n">
-        <x:f>SQRT((C83-C82)^2+(D83-D82)^2+(E83-E82)^2)</x:f>
+      <x:c r="F97" s="11" t="n">
+        <x:f>SQRT((C97-C96)^2+(D97-D96)^2+(E97-E96)^2)</x:f>
         <x:v>0.7000000000000002</x:v>
       </x:c>
-      <x:c r="G83" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" ht="32" customHeight="1">
-      <x:c r="A84" s="8" t="str">
+      <x:c r="G97" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="32" customHeight="1">
+      <x:c r="A98" s="8" t="str">
         <x:v>drop:LC1:E1:light:-1:L155</x:v>
       </x:c>
-      <x:c r="B84" s="8" t="n">
+      <x:c r="B98" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C84" s="11" t="n">
+      <x:c r="C98" s="11" t="n">
         <x:v>2.65</x:v>
       </x:c>
-      <x:c r="D84" s="11" t="n">
+      <x:c r="D98" s="11" t="n">
         <x:v>6.95</x:v>
       </x:c>
-      <x:c r="E84" s="11" t="n">
+      <x:c r="E98" s="11" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F84" s="11" t="n">
-        <x:f>SQRT((C84-C83)^2+(D84-D83)^2+(E84-E83)^2)</x:f>
+      <x:c r="F98" s="11" t="n">
+        <x:f>SQRT((C98-C97)^2+(D98-D97)^2+(E98-E97)^2)</x:f>
         <x:v>0.2999999999999998</x:v>
       </x:c>
-      <x:c r="G84" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" ht="32" customHeight="1">
-      <x:c r="A85" s="8" t="str">
+      <x:c r="G98" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="32" customHeight="1">
+      <x:c r="A99" s="8" t="str">
         <x:v>drop:LC1:E1:light:-1:L156</x:v>
       </x:c>
-      <x:c r="B85" s="8" t="n">
+      <x:c r="B99" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C85" s="11" t="n">
+      <x:c r="C99" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
-      <x:c r="D85" s="11" t="n">
+      <x:c r="D99" s="11" t="n">
         <x:v>5.988</x:v>
       </x:c>
-      <x:c r="E85" s="11" t="n">
+      <x:c r="E99" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
-      <x:c r="F85" s="11" t="n">
+      <x:c r="F99" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G85" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" ht="32" customHeight="1">
-      <x:c r="A86" s="8" t="str">
+      <x:c r="G99" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="32" customHeight="1">
+      <x:c r="A100" s="8" t="str">
         <x:v>drop:LC1:E1:light:-1:L156</x:v>
       </x:c>
-      <x:c r="B86" s="8" t="n">
+      <x:c r="B100" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C86" s="11" t="n">
+      <x:c r="C100" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
-      <x:c r="D86" s="11" t="n">
+      <x:c r="D100" s="11" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="E86" s="11" t="n">
+      <x:c r="E100" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
-      <x:c r="F86" s="11" t="n">
-        <x:f>SQRT((C86-C85)^2+(D86-D85)^2+(E86-E85)^2)</x:f>
+      <x:c r="F100" s="11" t="n">
+        <x:f>SQRT((C100-C99)^2+(D100-D99)^2+(E100-E99)^2)</x:f>
         <x:v>1.3880000000000008</x:v>
       </x:c>
-      <x:c r="G86" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" ht="32" customHeight="1">
-      <x:c r="A87" s="8" t="str">
+      <x:c r="G100" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="32" customHeight="1">
+      <x:c r="A101" s="8" t="str">
         <x:v>drop:LC1:E1:light:-1:L156</x:v>
       </x:c>
-      <x:c r="B87" s="8" t="n">
+      <x:c r="B101" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C87" s="11" t="n">
+      <x:c r="C101" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
-      <x:c r="D87" s="11" t="n">
+      <x:c r="D101" s="11" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="E87" s="11" t="n">
+      <x:c r="E101" s="11" t="n">
         <x:v>-7.245</x:v>
       </x:c>
-      <x:c r="F87" s="11" t="n">
-        <x:f>SQRT((C87-C86)^2+(D87-D86)^2+(E87-E86)^2)</x:f>
+      <x:c r="F101" s="11" t="n">
+        <x:f>SQRT((C101-C100)^2+(D101-D100)^2+(E101-E100)^2)</x:f>
         <x:v>0.11500000000000021</x:v>
       </x:c>
-      <x:c r="G87" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" ht="32" customHeight="1">
-      <x:c r="A88" s="8" t="str">
+      <x:c r="G101" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="32" customHeight="1">
+      <x:c r="A102" s="8" t="str">
         <x:v>drop:LC1:E1:light:-1:L158</x:v>
       </x:c>
-      <x:c r="B88" s="8" t="n">
+      <x:c r="B102" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C88" s="11" t="n">
+      <x:c r="C102" s="11" t="n">
         <x:v>34.725</x:v>
       </x:c>
-      <x:c r="D88" s="11" t="n">
+      <x:c r="D102" s="11" t="n">
         <x:v>5.988</x:v>
       </x:c>
-      <x:c r="E88" s="11" t="n">
+      <x:c r="E102" s="11" t="n">
         <x:v>-7.36</x:v>
       </x:c>
-      <x:c r="F88" s="11" t="n">
+      <x:c r="F102" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G88" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" ht="32" customHeight="1">
-      <x:c r="A89" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L158</x:v>
-      </x:c>
-      <x:c r="B89" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C89" s="11" t="n">
-        <x:v>34.725</x:v>
-      </x:c>
-      <x:c r="D89" s="11" t="n">
-        <x:v>4.6</x:v>
-      </x:c>
-      <x:c r="E89" s="11" t="n">
-        <x:v>-7.36</x:v>
-      </x:c>
-      <x:c r="F89" s="11" t="n">
-        <x:f>SQRT((C89-C88)^2+(D89-D88)^2+(E89-E88)^2)</x:f>
-        <x:v>1.3880000000000008</x:v>
-      </x:c>
-      <x:c r="G89" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" ht="32" customHeight="1">
-      <x:c r="A90" s="8" t="str">
-        <x:v>drop:LC1:E1:light:-1:L158</x:v>
-      </x:c>
-      <x:c r="B90" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C90" s="11" t="n">
-        <x:v>34.725</x:v>
-      </x:c>
-      <x:c r="D90" s="11" t="n">
-        <x:v>4.6</x:v>
-      </x:c>
-      <x:c r="E90" s="11" t="n">
-        <x:v>-7.245</x:v>
-      </x:c>
-      <x:c r="F90" s="11" t="n">
-        <x:f>SQRT((C90-C89)^2+(D90-D89)^2+(E90-E89)^2)</x:f>
-        <x:v>0.11500000000000021</x:v>
-      </x:c>
-      <x:c r="G90" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" ht="32" customHeight="1">
-      <x:c r="A91" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B91" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C91" s="11" t="n">
-        <x:v>48.895</x:v>
-      </x:c>
-      <x:c r="D91" s="11" t="n">
-        <x:v>1.85</x:v>
-      </x:c>
-      <x:c r="E91" s="11" t="n">
-        <x:v>-0.55</x:v>
-      </x:c>
-      <x:c r="F91" s="11" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G91" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" ht="32" customHeight="1">
-      <x:c r="A92" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B92" s="8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C92" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D92" s="11" t="n">
-        <x:v>1.85</x:v>
-      </x:c>
-      <x:c r="E92" s="11" t="n">
-        <x:v>-0.55</x:v>
-      </x:c>
-      <x:c r="F92" s="11" t="n">
-        <x:f>SQRT((C92-C91)^2+(D92-D91)^2+(E92-E91)^2)</x:f>
-        <x:v>0.1600000000000037</x:v>
-      </x:c>
-      <x:c r="G92" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" ht="32" customHeight="1">
-      <x:c r="A93" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B93" s="8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C93" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D93" s="11" t="n">
-        <x:v>1.85</x:v>
-      </x:c>
-      <x:c r="E93" s="11" t="n">
-        <x:v>-2.24</x:v>
-      </x:c>
-      <x:c r="F93" s="11" t="n">
-        <x:f>SQRT((C93-C92)^2+(D93-D92)^2+(E93-E92)^2)</x:f>
-        <x:v>1.6900000000000002</x:v>
-      </x:c>
-      <x:c r="G93" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" ht="32" customHeight="1">
-      <x:c r="A94" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B94" s="8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C94" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D94" s="11" t="n">
-        <x:v>4.33</x:v>
-      </x:c>
-      <x:c r="E94" s="11" t="n">
-        <x:v>-2.24</x:v>
-      </x:c>
-      <x:c r="F94" s="11" t="n">
-        <x:f>SQRT((C94-C93)^2+(D94-D93)^2+(E94-E93)^2)</x:f>
-        <x:v>2.48</x:v>
-      </x:c>
-      <x:c r="G94" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" ht="32" customHeight="1">
-      <x:c r="A95" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B95" s="8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C95" s="11" t="n">
-        <x:v>48.735</x:v>
-      </x:c>
-      <x:c r="D95" s="11" t="n">
-        <x:v>4.33</x:v>
-      </x:c>
-      <x:c r="E95" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F95" s="11" t="n">
-        <x:f>SQRT((C95-C94)^2+(D95-D94)^2+(E95-E94)^2)</x:f>
-        <x:v>1.0599999999999996</x:v>
-      </x:c>
-      <x:c r="G95" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="32" customHeight="1">
-      <x:c r="A96" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B96" s="8" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C96" s="11" t="n">
-        <x:v>53.016</x:v>
-      </x:c>
-      <x:c r="D96" s="11" t="n">
-        <x:v>4.33</x:v>
-      </x:c>
-      <x:c r="E96" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F96" s="11" t="n">
-        <x:f>SQRT((C96-C95)^2+(D96-D95)^2+(E96-E95)^2)</x:f>
-        <x:v>4.280999999999999</x:v>
-      </x:c>
-      <x:c r="G96" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" ht="32" customHeight="1">
-      <x:c r="A97" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B97" s="8" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C97" s="11" t="n">
-        <x:v>53.016</x:v>
-      </x:c>
-      <x:c r="D97" s="11" t="n">
-        <x:v>5.988</x:v>
-      </x:c>
-      <x:c r="E97" s="11" t="n">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="F97" s="11" t="n">
-        <x:f>SQRT((C97-C96)^2+(D97-D96)^2+(E97-E96)^2)</x:f>
-        <x:v>1.6580000000000004</x:v>
-      </x:c>
-      <x:c r="G97" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" ht="32" customHeight="1">
-      <x:c r="A98" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B98" s="8" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C98" s="11" t="n">
-        <x:v>53.016</x:v>
-      </x:c>
-      <x:c r="D98" s="11" t="n">
-        <x:v>5.988</x:v>
-      </x:c>
-      <x:c r="E98" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F98" s="11" t="n">
-        <x:f>SQRT((C98-C97)^2+(D98-D97)^2+(E98-E97)^2)</x:f>
-        <x:v>10.66</x:v>
-      </x:c>
-      <x:c r="G98" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" ht="32" customHeight="1">
-      <x:c r="A99" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B99" s="8" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C99" s="11" t="n">
-        <x:v>44.175</x:v>
-      </x:c>
-      <x:c r="D99" s="11" t="n">
-        <x:v>5.988</x:v>
-      </x:c>
-      <x:c r="E99" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F99" s="11" t="n">
-        <x:f>SQRT((C99-C98)^2+(D99-D98)^2+(E99-E98)^2)</x:f>
-        <x:v>8.841000000000001</x:v>
-      </x:c>
-      <x:c r="G99" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" ht="32" customHeight="1">
-      <x:c r="A100" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B100" s="8" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C100" s="11" t="n">
-        <x:v>44.175</x:v>
-      </x:c>
-      <x:c r="D100" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E100" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F100" s="11" t="n">
-        <x:f>SQRT((C100-C99)^2+(D100-D99)^2+(E100-E99)^2)</x:f>
-        <x:v>1.0519999999999996</x:v>
-      </x:c>
-      <x:c r="G100" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" ht="32" customHeight="1">
-      <x:c r="A101" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B101" s="8" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C101" s="11" t="n">
-        <x:v>43.535</x:v>
-      </x:c>
-      <x:c r="D101" s="11" t="n">
-        <x:v>7.04</x:v>
-      </x:c>
-      <x:c r="E101" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F101" s="11" t="n">
-        <x:f>SQRT((C101-C100)^2+(D101-D100)^2+(E101-E100)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
-      </x:c>
-      <x:c r="G101" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="32" customHeight="1">
-      <x:c r="A102" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
-      </x:c>
-      <x:c r="B102" s="8" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C102" s="11" t="n">
-        <x:v>43.455</x:v>
-      </x:c>
-      <x:c r="D102" s="11" t="n">
-        <x:v>6.950412371134024</x:v>
-      </x:c>
-      <x:c r="E102" s="11" t="n">
-        <x:v>7.36</x:v>
-      </x:c>
-      <x:c r="F102" s="11" t="n">
-        <x:f>SQRT((C102-C101)^2+(D102-D101)^2+(E102-E101)^2)</x:f>
-        <x:v>0.12010804821421249</x:v>
-      </x:c>
       <x:c r="G102" s="8" t="str">
         <x:v>Retired</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="32" customHeight="1">
       <x:c r="A103" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>drop:LC1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B103" s="8" t="n">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C103" s="11" t="n">
-        <x:v>40.574999999999996</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D103" s="11" t="n">
-        <x:v>9.269999999999994</x:v>
+        <x:v>4.6</x:v>
       </x:c>
       <x:c r="E103" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.36</x:v>
       </x:c>
       <x:c r="F103" s="11" t="n">
         <x:f>SQRT((C103-C102)^2+(D103-D102)^2+(E103-E102)^2)</x:f>
-        <x:v>3.6979571073753776</x:v>
+        <x:v>1.3880000000000008</x:v>
       </x:c>
       <x:c r="G103" s="8" t="str">
         <x:v>Retired</x:v>
@@ -4878,23 +4878,23 @@
     </x:row>
     <x:row r="104" ht="32" customHeight="1">
       <x:c r="A104" s="8" t="str">
-        <x:v>trunk:LC1:E1:light:1</x:v>
+        <x:v>drop:LC1:E1:light:-1:L158</x:v>
       </x:c>
       <x:c r="B104" s="8" t="n">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C104" s="11" t="n">
-        <x:v>37.695</x:v>
+        <x:v>34.725</x:v>
       </x:c>
       <x:c r="D104" s="11" t="n">
-        <x:v>6.950412371134018</x:v>
+        <x:v>4.6</x:v>
       </x:c>
       <x:c r="E104" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-7.245</x:v>
       </x:c>
       <x:c r="F104" s="11" t="n">
         <x:f>SQRT((C104-C103)^2+(D104-D103)^2+(E104-E103)^2)</x:f>
-        <x:v>3.697957107375376</x:v>
+        <x:v>0.11500000000000021</x:v>
       </x:c>
       <x:c r="G104" s="8" t="str">
         <x:v>Retired</x:v>
@@ -4905,20 +4905,20 @@
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B105" s="8" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C105" s="11" t="n">
-        <x:v>37.615</x:v>
+        <x:v>48.895</x:v>
       </x:c>
       <x:c r="D105" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E105" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="F105" s="11" t="n">
-        <x:f>SQRT((C105-C104)^2+(D105-D104)^2+(E105-E104)^2)</x:f>
-        <x:v>0.12010804821421713</x:v>
+        <x:f>0</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G105" s="8" t="str">
         <x:v>Retired</x:v>
@@ -4929,20 +4929,20 @@
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B106" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C106" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D106" s="11" t="n">
-        <x:v>7.04</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E106" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="F106" s="11" t="n">
         <x:f>SQRT((C106-C105)^2+(D106-D105)^2+(E106-E105)^2)</x:f>
-        <x:v>0.6400000000000006</x:v>
+        <x:v>0.1600000000000037</x:v>
       </x:c>
       <x:c r="G106" s="8" t="str">
         <x:v>Retired</x:v>
@@ -4953,20 +4953,20 @@
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B107" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C107" s="11" t="n">
-        <x:v>36.975</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
-        <x:v>5.988</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="E107" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F107" s="11" t="n">
         <x:f>SQRT((C107-C106)^2+(D107-D106)^2+(E107-E106)^2)</x:f>
-        <x:v>1.0519999999999996</x:v>
+        <x:v>1.6900000000000002</x:v>
       </x:c>
       <x:c r="G107" s="8" t="str">
         <x:v>Retired</x:v>
@@ -4977,20 +4977,20 @@
         <x:v>trunk:LC1:E1:light:1</x:v>
       </x:c>
       <x:c r="B108" s="8" t="n">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C108" s="11" t="n">
-        <x:v>16.725</x:v>
+        <x:v>48.735</x:v>
       </x:c>
       <x:c r="D108" s="11" t="n">
-        <x:v>5.988</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="E108" s="11" t="n">
-        <x:v>7.36</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="F108" s="11" t="n">
         <x:f>SQRT((C108-C107)^2+(D108-D107)^2+(E108-E107)^2)</x:f>
-        <x:v>20.25</x:v>
+        <x:v>2.48</x:v>
       </x:c>
       <x:c r="G108" s="8" t="str">
         <x:v>Retired</x:v>
@@ -4998,155 +4998,491 @@
     </x:row>
     <x:row r="109" ht="32" customHeight="1">
       <x:c r="A109" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B109" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C109" s="11" t="n">
+        <x:v>48.735</x:v>
+      </x:c>
+      <x:c r="D109" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E109" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F109" s="11" t="n">
+        <x:f>SQRT((C109-C108)^2+(D109-D108)^2+(E109-E108)^2)</x:f>
+        <x:v>1.0599999999999996</x:v>
+      </x:c>
+      <x:c r="G109" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="32" customHeight="1">
+      <x:c r="A110" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B110" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C110" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D110" s="11" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="E110" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F110" s="11" t="n">
+        <x:f>SQRT((C110-C109)^2+(D110-D109)^2+(E110-E109)^2)</x:f>
+        <x:v>4.280999999999999</x:v>
+      </x:c>
+      <x:c r="G110" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="32" customHeight="1">
+      <x:c r="A111" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B111" s="8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C111" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D111" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E111" s="11" t="n">
+        <x:v>-3.3</x:v>
+      </x:c>
+      <x:c r="F111" s="11" t="n">
+        <x:f>SQRT((C111-C110)^2+(D111-D110)^2+(E111-E110)^2)</x:f>
+        <x:v>1.6580000000000004</x:v>
+      </x:c>
+      <x:c r="G111" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="32" customHeight="1">
+      <x:c r="A112" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B112" s="8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C112" s="11" t="n">
+        <x:v>53.016</x:v>
+      </x:c>
+      <x:c r="D112" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E112" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F112" s="11" t="n">
+        <x:f>SQRT((C112-C111)^2+(D112-D111)^2+(E112-E111)^2)</x:f>
+        <x:v>10.66</x:v>
+      </x:c>
+      <x:c r="G112" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="32" customHeight="1">
+      <x:c r="A113" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B113" s="8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C113" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D113" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E113" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F113" s="11" t="n">
+        <x:f>SQRT((C113-C112)^2+(D113-D112)^2+(E113-E112)^2)</x:f>
+        <x:v>8.841000000000001</x:v>
+      </x:c>
+      <x:c r="G113" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="32" customHeight="1">
+      <x:c r="A114" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B114" s="8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C114" s="11" t="n">
+        <x:v>44.175</x:v>
+      </x:c>
+      <x:c r="D114" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E114" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F114" s="11" t="n">
+        <x:f>SQRT((C114-C113)^2+(D114-D113)^2+(E114-E113)^2)</x:f>
+        <x:v>1.0519999999999996</x:v>
+      </x:c>
+      <x:c r="G114" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="32" customHeight="1">
+      <x:c r="A115" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B115" s="8" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C115" s="11" t="n">
+        <x:v>43.535</x:v>
+      </x:c>
+      <x:c r="D115" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E115" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F115" s="11" t="n">
+        <x:f>SQRT((C115-C114)^2+(D115-D114)^2+(E115-E114)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G115" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="32" customHeight="1">
+      <x:c r="A116" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B116" s="8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C116" s="11" t="n">
+        <x:v>43.455</x:v>
+      </x:c>
+      <x:c r="D116" s="11" t="n">
+        <x:v>6.950412371134024</x:v>
+      </x:c>
+      <x:c r="E116" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F116" s="11" t="n">
+        <x:f>SQRT((C116-C115)^2+(D116-D115)^2+(E116-E115)^2)</x:f>
+        <x:v>0.12010804821421249</x:v>
+      </x:c>
+      <x:c r="G116" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="32" customHeight="1">
+      <x:c r="A117" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B117" s="8" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C117" s="11" t="n">
+        <x:v>40.574999999999996</x:v>
+      </x:c>
+      <x:c r="D117" s="11" t="n">
+        <x:v>9.269999999999994</x:v>
+      </x:c>
+      <x:c r="E117" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F117" s="11" t="n">
+        <x:f>SQRT((C117-C116)^2+(D117-D116)^2+(E117-E116)^2)</x:f>
+        <x:v>3.6979571073753776</x:v>
+      </x:c>
+      <x:c r="G117" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="32" customHeight="1">
+      <x:c r="A118" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B118" s="8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C118" s="11" t="n">
+        <x:v>37.695</x:v>
+      </x:c>
+      <x:c r="D118" s="11" t="n">
+        <x:v>6.950412371134018</x:v>
+      </x:c>
+      <x:c r="E118" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F118" s="11" t="n">
+        <x:f>SQRT((C118-C117)^2+(D118-D117)^2+(E118-E117)^2)</x:f>
+        <x:v>3.697957107375376</x:v>
+      </x:c>
+      <x:c r="G118" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="32" customHeight="1">
+      <x:c r="A119" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B119" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C119" s="11" t="n">
+        <x:v>37.615</x:v>
+      </x:c>
+      <x:c r="D119" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E119" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F119" s="11" t="n">
+        <x:f>SQRT((C119-C118)^2+(D119-D118)^2+(E119-E118)^2)</x:f>
+        <x:v>0.12010804821421713</x:v>
+      </x:c>
+      <x:c r="G119" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="32" customHeight="1">
+      <x:c r="A120" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B120" s="8" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C120" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D120" s="11" t="n">
+        <x:v>7.04</x:v>
+      </x:c>
+      <x:c r="E120" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F120" s="11" t="n">
+        <x:f>SQRT((C120-C119)^2+(D120-D119)^2+(E120-E119)^2)</x:f>
+        <x:v>0.6400000000000006</x:v>
+      </x:c>
+      <x:c r="G120" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="32" customHeight="1">
+      <x:c r="A121" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B121" s="8" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C121" s="11" t="n">
+        <x:v>36.975</x:v>
+      </x:c>
+      <x:c r="D121" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E121" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F121" s="11" t="n">
+        <x:f>SQRT((C121-C120)^2+(D121-D120)^2+(E121-E120)^2)</x:f>
+        <x:v>1.0519999999999996</x:v>
+      </x:c>
+      <x:c r="G121" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="32" customHeight="1">
+      <x:c r="A122" s="8" t="str">
+        <x:v>trunk:LC1:E1:light:1</x:v>
+      </x:c>
+      <x:c r="B122" s="8" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C122" s="11" t="n">
+        <x:v>16.725</x:v>
+      </x:c>
+      <x:c r="D122" s="11" t="n">
+        <x:v>5.988</x:v>
+      </x:c>
+      <x:c r="E122" s="11" t="n">
+        <x:v>7.36</x:v>
+      </x:c>
+      <x:c r="F122" s="11" t="n">
+        <x:f>SQRT((C122-C121)^2+(D122-D121)^2+(E122-E121)^2)</x:f>
+        <x:v>20.25</x:v>
+      </x:c>
+      <x:c r="G122" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="32" customHeight="1">
+      <x:c r="A123" s="8" t="str">
         <x:v>drop:LC1:E1:light:1:L157</x:v>
       </x:c>
-      <x:c r="B109" s="8" t="n">
+      <x:c r="B123" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C109" s="11" t="n">
+      <x:c r="C123" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
-      <x:c r="D109" s="11" t="n">
+      <x:c r="D123" s="11" t="n">
         <x:v>5.988</x:v>
       </x:c>
-      <x:c r="E109" s="11" t="n">
+      <x:c r="E123" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F109" s="11" t="n">
+      <x:c r="F123" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G109" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" ht="32" customHeight="1">
-      <x:c r="A110" s="8" t="str">
+      <x:c r="G123" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="32" customHeight="1">
+      <x:c r="A124" s="8" t="str">
         <x:v>drop:LC1:E1:light:1:L157</x:v>
       </x:c>
-      <x:c r="B110" s="8" t="n">
+      <x:c r="B124" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C110" s="11" t="n">
+      <x:c r="C124" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
-      <x:c r="D110" s="11" t="n">
+      <x:c r="D124" s="11" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="E110" s="11" t="n">
+      <x:c r="E124" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F110" s="11" t="n">
-        <x:f>SQRT((C110-C109)^2+(D110-D109)^2+(E110-E109)^2)</x:f>
+      <x:c r="F124" s="11" t="n">
+        <x:f>SQRT((C124-C123)^2+(D124-D123)^2+(E124-E123)^2)</x:f>
         <x:v>1.3880000000000008</x:v>
       </x:c>
-      <x:c r="G110" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" ht="32" customHeight="1">
-      <x:c r="A111" s="8" t="str">
+      <x:c r="G124" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="32" customHeight="1">
+      <x:c r="A125" s="8" t="str">
         <x:v>drop:LC1:E1:light:1:L157</x:v>
       </x:c>
-      <x:c r="B111" s="8" t="n">
+      <x:c r="B125" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C111" s="11" t="n">
+      <x:c r="C125" s="11" t="n">
         <x:v>16.725</x:v>
       </x:c>
-      <x:c r="D111" s="11" t="n">
+      <x:c r="D125" s="11" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="E111" s="11" t="n">
+      <x:c r="E125" s="11" t="n">
         <x:v>7.245</x:v>
       </x:c>
-      <x:c r="F111" s="11" t="n">
-        <x:f>SQRT((C111-C110)^2+(D111-D110)^2+(E111-E110)^2)</x:f>
+      <x:c r="F125" s="11" t="n">
+        <x:f>SQRT((C125-C124)^2+(D125-D124)^2+(E125-E124)^2)</x:f>
         <x:v>0.11500000000000021</x:v>
       </x:c>
-      <x:c r="G111" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" ht="32" customHeight="1">
-      <x:c r="A112" s="8" t="str">
+      <x:c r="G125" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="32" customHeight="1">
+      <x:c r="A126" s="8" t="str">
         <x:v>drop:LC1:E1:light:1:L159</x:v>
       </x:c>
-      <x:c r="B112" s="8" t="n">
+      <x:c r="B126" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C112" s="11" t="n">
+      <x:c r="C126" s="11" t="n">
         <x:v>34.725</x:v>
       </x:c>
-      <x:c r="D112" s="11" t="n">
+      <x:c r="D126" s="11" t="n">
         <x:v>5.988</x:v>
       </x:c>
-      <x:c r="E112" s="11" t="n">
+      <x:c r="E126" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F112" s="11" t="n">
+      <x:c r="F126" s="11" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G112" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" ht="32" customHeight="1">
-      <x:c r="A113" s="8" t="str">
+      <x:c r="G126" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="32" customHeight="1">
+      <x:c r="A127" s="8" t="str">
         <x:v>drop:LC1:E1:light:1:L159</x:v>
       </x:c>
-      <x:c r="B113" s="8" t="n">
+      <x:c r="B127" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C113" s="11" t="n">
+      <x:c r="C127" s="11" t="n">
         <x:v>34.725</x:v>
       </x:c>
-      <x:c r="D113" s="11" t="n">
+      <x:c r="D127" s="11" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="E113" s="11" t="n">
+      <x:c r="E127" s="11" t="n">
         <x:v>7.36</x:v>
       </x:c>
-      <x:c r="F113" s="11" t="n">
-        <x:f>SQRT((C113-C112)^2+(D113-D112)^2+(E113-E112)^2)</x:f>
+      <x:c r="F127" s="11" t="n">
+        <x:f>SQRT((C127-C126)^2+(D127-D126)^2+(E127-E126)^2)</x:f>
         <x:v>1.3880000000000008</x:v>
       </x:c>
-      <x:c r="G113" s="8" t="str">
-        <x:v>Retired</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" ht="32" customHeight="1">
-      <x:c r="A114" s="8" t="str">
+      <x:c r="G127" s="8" t="str">
+        <x:v>Retired</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="32" customHeight="1">
+      <x:c r="A128" s="8" t="str">
         <x:v>drop:LC1:E1:light:1:L159</x:v>
       </x:c>
-      <x:c r="B114" s="8" t="n">
+      <x:c r="B128" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C114" s="11" t="n">
+      <x:c r="C128" s="11" t="n">
         <x:v>34.725</x:v>
       </x:c>
-      <x:c r="D114" s="11" t="n">
+      <x:c r="D128" s="11" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="E114" s="11" t="n">
+      <x:c r="E128" s="11" t="n">
         <x:v>7.245</x:v>
       </x:c>
-      <x:c r="F114" s="11" t="n">
-        <x:f>SQRT((C114-C113)^2+(D114-D113)^2+(E114-E113)^2)</x:f>
+      <x:c r="F128" s="11" t="n">
+        <x:f>SQRT((C128-C127)^2+(D128-D127)^2+(E128-E127)^2)</x:f>
         <x:v>0.11500000000000021</x:v>
       </x:c>
-      <x:c r="G114" s="8" t="str">
+      <x:c r="G128" s="8" t="str">
         <x:v>Retired</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G7:G114">
+  <x:conditionalFormatting sqref="G7:G128">
     <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Retired"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad2531560a5b4e59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5445e4c65a084335"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R309fbb352740486f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R560c49c973d24ae4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="Rd3e8b4c22b9f4b82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R3ca4afe8b0da44e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rdbc649d68b084a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8091ca5c3b1e46c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R4a42dbcc9ac242b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc7cded3d549144cb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-25T12:31:42.928Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-31T15:58:16.965Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>6638c6d858c0c15d03f1b8c7f8d4371e61b16cbc58edb9c36dd4e72b917f5303</x:v>
+        <x:v>7958b4809b6199a78823ea47abdd37329f78f9de03404b0f973483495d74be9e</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>8efd0e5d2f1745401819248f5cd349c1ca2995df2b2938bff0ddd27c9679b4c8</x:v>
+        <x:v>de942b6ea94208f140cd0ec1bb6d7282f467a001cb150dd4c584a870ba9c4c2b</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0699a86fc43c4523"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55b0762530094371"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a8590e629b64919"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5d961824e8348e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5482,7 +5482,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5445e4c65a084335"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R984e7fb615c0451d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rdbc649d68b084a60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R8091ca5c3b1e46c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R4a42dbcc9ac242b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc7cded3d549144cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd6cac1189a0148d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R53a8e7542a4944ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6ca1bdc5358041d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb9aef3f73581424a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-31T15:58:16.965Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>7958b4809b6199a78823ea47abdd37329f78f9de03404b0f973483495d74be9e</x:v>
+        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>de942b6ea94208f140cd0ec1bb6d7282f467a001cb150dd4c584a870ba9c4c2b</x:v>
+        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55b0762530094371"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd481dc063a324cf2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5d961824e8348e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c6951afd5144524"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5482,7 +5482,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R984e7fb615c0451d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4b5ef8e6a644be0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd6cac1189a0148d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R53a8e7542a4944ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6ca1bdc5358041d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb9aef3f73581424a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R76c058c228404184"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="Re101b6b252964334"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R10bd1285cbac432f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="R7adeed208a4247bc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-11-01T00:50:08.502Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
+        <x:v>b59c831ec1c00c49183c1e83c86ee8d801e0152690935057f3be6f551a8b788b</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
+        <x:v>2a343075b78e07a39b50033e252aeaec71194df376aa048789dba03e95d6e972</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -972,7 +972,7 @@
         <x:v>E1</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>2.6800000008940703</x:v>
+        <x:v>5.313000000894069</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
         <x:v>4.762499999552966</x:v>
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd481dc063a324cf2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff44f05d88c94f61"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1614,7 +1614,7 @@
       </x:c>
       <x:c r="I7" s="11" t="n">
         <x:f>SUMIF('Route Points'!$A$7:$A$128,A7,'Route Points'!$F$7:$F$128)</x:f>
-        <x:v>68.64513031028511</x:v>
+        <x:v>66.01213031028512</x:v>
       </x:c>
       <x:c r="J7" s="11"/>
       <x:c r="K7" s="11" t="str">
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c6951afd5144524"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R343f135704894597"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2988,7 +2988,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>2.6800000008940703</x:v>
+        <x:v>5.313000000894069</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>5.988</x:v>
@@ -2998,7 +2998,7 @@
       </x:c>
       <x:c r="F25" s="11" t="n">
         <x:f>SQRT((C25-C24)^2+(D25-D24)^2+(E25-E24)^2)</x:f>
-        <x:v>2.7949999991059293</x:v>
+        <x:v>0.16199999910593021</x:v>
       </x:c>
       <x:c r="G25" s="8" t="str">
         <x:v>Current</x:v>
@@ -3012,7 +3012,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
-        <x:v>2.6800000008940703</x:v>
+        <x:v>5.313000000894069</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>5.988</x:v>
@@ -3036,7 +3036,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
-        <x:v>2.5920000008940702</x:v>
+        <x:v>5.225000000894069</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
         <x:v>5.988</x:v>
@@ -3060,7 +3060,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
-        <x:v>2.5920000008940702</x:v>
+        <x:v>5.225000000894069</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
         <x:v>5.988</x:v>
@@ -3084,7 +3084,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>2.5920000008940702</x:v>
+        <x:v>5.225000000894069</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
         <x:v>4.9</x:v>
@@ -3108,7 +3108,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>2.5920000008940702</x:v>
+        <x:v>5.225000000894069</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
         <x:v>4.9</x:v>
@@ -3132,7 +3132,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>2.6800000008940703</x:v>
+        <x:v>5.313000000894069</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
         <x:v>4.9</x:v>
@@ -3156,7 +3156,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
-        <x:v>2.6800000008940703</x:v>
+        <x:v>5.313000000894069</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
         <x:v>4.762499999552966</x:v>
@@ -5482,7 +5482,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4b5ef8e6a644be0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97d177f130f544c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/electrical-grid/categories/exit-signs/register.xlsx
+++ b/docs/electrical-grid/categories/exit-signs/register.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="Rd6cac1189a0148d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R53a8e7542a4944ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R6ca1bdc5358041d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rb9aef3f73581424a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R86690f87d48a45e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="2" r:id="R20fdc07fba1349db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electrical Lines" sheetId="3" r:id="R7e0086fecc8940db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route Points" sheetId="4" r:id="Rc9cbc9674b5a4e37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,7 +493,7 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-10-31T16:19:36.678Z.</x:v>
+        <x:v>Exit signs. E1 maintained exit-sign group. Emergency supply and duration require separate design. Model snapshot: 2026-11-01T01:42:20.339Z.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -576,7 +576,7 @@
         <x:v>Source layout SHA-256</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>3cdbadaba0ffc908418f454ec3a56c6c112739ccae548d5038c524ed0fb572ae</x:v>
+        <x:v>50118e5af402ff0efaabf2d570ac3f0129d03efc89e10e7eeb51b8d67485750c</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
@@ -584,7 +584,7 @@
         <x:v>Source systems SHA-256</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>19f49808ff7b94351ad8e2bad9b30d5c978e8d5e96c5f164a91146ca0afcd5ac</x:v>
+        <x:v>0fb0ba42a427dbbe355fa325c0efcf0641bfb0dae62bd4f360bc65584cfd7d81</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1320,7 +1320,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd481dc063a324cf2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85fd4141acb04756"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,7 +2454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c6951afd5144524"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7589b18248e4bbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5482,7 +5482,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4b5ef8e6a644be0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bb1730bdd354db0"/>
   </x:tableParts>
 </x:worksheet>
 </file>